--- a/resultados/rodada05/quadro_subsetores_v04.xlsx
+++ b/resultados/rodada05/quadro_subsetores_v04.xlsx
@@ -12,20 +12,21 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="v03_x_v04" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="passos_v03_v04" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d18_latentes" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tust_latentes_versoes" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="realocacao_E4" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="insumos_nao_energeticos" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tust_geracao" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pisos_vbp" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reequilibrio_RAS" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reequilibrio_insumos" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variantes_resumo" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variantes_subsetores" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gas_por_comprador" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gas_por_grupo" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="checagens" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="componentes_bloco" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="niveis_emissoes" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="d18_eob_implicito_versoes" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tust_latentes_versoes" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="realocacao_E4" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="insumos_nao_energeticos" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="tust_geracao" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="pisos_vbp" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reequilibrio_RAS" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="reequilibrio_insumos" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variantes_resumo" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="variantes_subsetores" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gas_por_comprador" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="gas_por_grupo" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="checagens" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="componentes_bloco" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="niveis_emissoes" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -497,6 +498,970 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:G33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="20" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>versao</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regiao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>subsetor</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>VBP</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>TUST</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>TUST / VBP</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>remuneracoes / VBP</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>S38_HID</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>2478.318234397699</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>511.3643184267204</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.2063352120519729</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.06691592618436512</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>S38_EOL</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>933.8642937913977</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>185.2022746789912</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.1983181881032072</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.06691592618436512</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>S38_SOL</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="2" t="inlineStr"/>
+      <c r="G4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>S38_BIO</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>14.39610458122591</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>2.399314045532176</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.1666641161152124</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.06520851157769522</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>S38_CAR</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>675.0415899274054</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>92.31156187608121</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.1367494436691056</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.0654537245601737</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>S38_GN</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>48.96694328784385</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>6.138188599700058</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.1253537220736398</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.02007477785530953</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>S38_PET</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="2" t="inlineStr"/>
+      <c r="G8" s="2" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>S38_NUC</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="2" t="inlineStr"/>
+      <c r="G9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>S38_HID</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>45236.76699106405</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>8578.497122829611</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.189635504334874</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.1384575223270457</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>S38_EOL</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>6555.543617866584</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>1134.414365639333</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.1730465742837225</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0.1384575223270457</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>S38_SOL</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>969.0298002286172</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>103.3584063315243</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.1066617417824917</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.1384575223270457</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>S38_BIO</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>272.6706285168253</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>41.76637322175468</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.1531751822663858</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0.1356358917117955</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>S38_CAR</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>2100.294455021196</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>263.9684706987219</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.1256816490981299</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0.1235436406794368</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>S38_GN</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>10981.93425757629</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>1095.545089944344</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0.09975884614211217</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0.04153725669811374</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>S38_PET</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>4066.596731580632</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>46.54031439396415</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.01144453641850898</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0.04153725669811372</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>v03</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>S38_NUC</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>2981.204148523032</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>380.2079171537242</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0.1275350154541041</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0.1384575223270457</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>S38_HID</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>2549.693654128071</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>471.3357766749352</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0.1848597677261427</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0.06504251030705867</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>S38_EOL</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>960.7595306562334</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>170.7050234681092</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.1776771585617387</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>0.06504251030705865</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>S38_SOL</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr"/>
+      <c r="G20" s="2" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>S38_BIO</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="n">
+        <v>14.81071154844496</v>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>2.211500701920889</v>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>0.1493176539619451</v>
+      </c>
+      <c r="G21" s="2" t="n">
+        <v>0.06342935618341794</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>S38_CAR</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="n">
+        <v>694.4827481078984</v>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>85.08560363930458</v>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>0.1225165115636325</v>
+      </c>
+      <c r="G22" s="2" t="n">
+        <v>0.06366103180122638</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>S38_GN</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="n">
+        <v>48.96694328784385</v>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>5.657703885007092</v>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>0.115541291841503</v>
+      </c>
+      <c r="G23" s="2" t="n">
+        <v>0.0195127530921176</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>S38_PET</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>S38_NUC</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>S38_HID</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="n">
+        <v>46660.99212599756</v>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>7906.990101563006</v>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>0.1694561075815094</v>
+      </c>
+      <c r="G26" s="2" t="n">
+        <v>0.1345132085983258</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>S38_EOL</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="n">
+        <v>6761.937014537989</v>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>1045.614754163652</v>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>0.1546324303103693</v>
+      </c>
+      <c r="G27" s="2" t="n">
+        <v>0.1345132085983258</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>S38_SOL</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="n">
+        <v>999.538536590299</v>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>95.26772394686297</v>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>0.09531170681207289</v>
+      </c>
+      <c r="G28" s="2" t="n">
+        <v>0.1345132085983258</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>S38_BIO</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="n">
+        <v>281.255334907724</v>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>38.49698786559352</v>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>0.136875582744853</v>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>0.1318556299518232</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>S38_CAR</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="n">
+        <v>2166.419696778494</v>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>243.3055644892561</v>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>0.1123076774325196</v>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>0.1204664325288654</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>S38_GN</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="n">
+        <v>10981.93425757629</v>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>1009.788085019323</v>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>0.09194992988805079</v>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>0.04035396257949774</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>S38_PET</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="n">
+        <v>4066.596731580632</v>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>42.89723479155547</v>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>0.01054868176586614</v>
+      </c>
+      <c r="G32" s="2" t="n">
+        <v>0.04035396257949776</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>S38_NUC</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="n">
+        <v>3075.0637711953</v>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>350.4460273664763</v>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>0.1139638243112777</v>
+      </c>
+      <c r="G33" s="2" t="n">
+        <v>0.1345132085983258</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:P14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -1283,7 +2248,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2589,7 +3554,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15141,7 +16106,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -15477,7 +16442,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'OK': 37, 'ALERTA': 3}</t>
+          <t>{'OK': 38, 'ALERTA': 3}</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -15744,7 +16709,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -29392,7 +30357,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39084,7 +40049,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -39526,13 +40491,13 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F329"/>
+  <dimension ref="A1:F330"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
@@ -44074,7 +45039,7 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>niveis_residuo_nao_negativo</t>
+          <t>realocacao_co2e_proporcao_residuo</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
@@ -44083,14 +45048,14 @@
         </is>
       </c>
       <c r="C167" s="2" t="n">
-        <v>0</v>
+        <v>1.387778780781446e-17</v>
       </c>
       <c r="D167" s="2" t="n">
-        <v>0</v>
+        <v>1e-09</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>RS co2e (residuo): identificado 3862147.8290, resíduo 1975857.7254; RB co2e (residuo): identificado 34828615.1621, resíduo 49689733.8945</t>
+          <t>máx |parcela retirada de cada subsetor do resíduo − parcela dele no VBP dos subsetores do resíduo|</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -44102,7 +45067,7 @@
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>EOB_nao_negativo_subsetores</t>
+          <t>niveis_residuo_nao_negativo</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
@@ -44118,7 +45083,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>todos ≥ 0</t>
+          <t>RS co2e (residuo): identificado 3862147.8290, resíduo 1975857.7254; RB co2e (residuo): identificado 34828615.1621, resíduo 49689733.8945</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -44130,7 +45095,7 @@
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>subsetores_producao_zero_zerados</t>
+          <t>EOB_nao_negativo_subsetores</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
@@ -44139,14 +45104,14 @@
         </is>
       </c>
       <c r="C169" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D169" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>3 subsetor(es) com produção zero: RS_S38_SOL, RS_S38_PET, RS_S38_NUC</t>
+          <t>todos ≥ 0</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -44158,7 +45123,7 @@
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>L_nao_negativa</t>
+          <t>subsetores_producao_zero_zerados</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
@@ -44167,12 +45132,16 @@
         </is>
       </c>
       <c r="C170" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D170" s="2" t="n">
-        <v>-1e-10</v>
-      </c>
-      <c r="E170" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>3 subsetor(es) com produção zero: RS_S38_SOL, RS_S38_PET, RS_S38_NUC</t>
+        </is>
+      </c>
       <c r="F170" t="inlineStr">
         <is>
           <t>v04_E4</t>
@@ -44182,7 +45151,7 @@
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>L_diagonal_maior_igual_1</t>
+          <t>L_nao_negativa</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
@@ -44191,10 +45160,10 @@
         </is>
       </c>
       <c r="C171" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D171" s="2" t="n">
-        <v>1</v>
+        <v>-1e-10</v>
       </c>
       <c r="E171" t="inlineStr"/>
       <c r="F171" t="inlineStr">
@@ -44206,7 +45175,7 @@
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>A_soma_colunas_menor_1</t>
+          <t>L_diagonal_maior_igual_1</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
@@ -44215,16 +45184,12 @@
         </is>
       </c>
       <c r="C172" s="2" t="n">
-        <v>0.8501168940529817</v>
+        <v>1</v>
       </c>
       <c r="D172" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>Σ coeficientes técnicos de cada coluna (inclui latentes)</t>
-        </is>
-      </c>
+      <c r="E172" t="inlineStr"/>
       <c r="F172" t="inlineStr">
         <is>
           <t>v04_E4</t>
@@ -44234,7 +45199,7 @@
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>RAS_convergencia</t>
+          <t>A_soma_colunas_menor_1</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
@@ -44243,14 +45208,14 @@
         </is>
       </c>
       <c r="C173" s="2" t="n">
-        <v>22</v>
+        <v>0.8501168940529817</v>
       </c>
       <c r="D173" s="2" t="n">
-        <v>20000</v>
+        <v>1</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>linhas RS S38: necessário, convergiu em 22 iterações, erro 4.98e-09 (inicial 4.21e-01); linhas RB S38: necessário, convergiu em 21 iterações, erro 8.56e-09 (inicial 1.38e+00); reequilibrio_EOB RS (η = 0.1): necessário, convergiu em 7 iterações, erro 1.43e-09 (inicial 1.26e+02); reequilibrio_EOB RB (η = 0.1): necessário, convergiu em 8 iterações, erro 1.15e-09 (inicial 2.46e+03)</t>
+          <t>Σ coeficientes técnicos de cada coluna (inclui latentes)</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -44262,7 +45227,7 @@
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>roteamento_vendas_geracao_igual_E</t>
+          <t>RAS_convergencia</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
@@ -44271,14 +45236,14 @@
         </is>
       </c>
       <c r="C174" s="2" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>22</v>
       </c>
       <c r="D174" s="2" t="n">
-        <v>1e-06</v>
+        <v>20000</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>Σ vendas da geração de r dentro do bloco = E_r = F_r − T_r − G_r</t>
+          <t>linhas RS S38: necessário, convergiu em 22 iterações, erro 4.98e-09 (inicial 4.21e-01); linhas RB S38: necessário, convergiu em 21 iterações, erro 8.56e-09 (inicial 1.38e+00); reequilibrio_EOB RS (η = 0.1): necessário, convergiu em 7 iterações, erro 1.43e-09 (inicial 1.26e+02); reequilibrio_EOB RB (η = 0.1): necessário, convergiu em 8 iterações, erro 1.15e-09 (inicial 2.46e+03)</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -44290,7 +45255,7 @@
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>roteamento_vendas_transmissao_igual_T</t>
+          <t>roteamento_vendas_geracao_igual_E</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
@@ -44299,14 +45264,14 @@
         </is>
       </c>
       <c r="C175" s="2" t="n">
-        <v>0</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="D175" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>Σ vendas da transmissão de r dentro do bloco = T_r</t>
+          <t>Σ vendas da geração de r dentro do bloco = E_r = F_r − T_r − G_r</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -44318,7 +45283,7 @@
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>roteamento_geracao_e_transmissao_nao_vendem_fora</t>
+          <t>roteamento_vendas_transmissao_igual_T</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
@@ -44334,7 +45299,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>Σ |vendas| da geração e da transmissão fora do bloco e à demanda final (Seção 6.4)</t>
+          <t>Σ vendas da transmissão de r dentro do bloco = T_r</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -44346,7 +45311,7 @@
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>roteamento_fracao_transmissao</t>
+          <t>roteamento_geracao_e_transmissao_nao_vendem_fora</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -44355,14 +45320,14 @@
         </is>
       </c>
       <c r="C177" s="2" t="n">
-        <v>8.173395242890144e-17</v>
+        <v>0</v>
       </c>
       <c r="D177" s="2" t="n">
-        <v>1e-09</v>
+        <v>1e-06</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>fração da transmissão paga pela distribuição e pela geração das regiões desagregadas (o S38 agregado de região não desagregada recebe a sua parte inteira)</t>
+          <t>Σ |vendas| da geração e da transmissão fora do bloco e à demanda final (Seção 6.4)</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -44374,7 +45339,7 @@
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>bloco_fluxos_regionais_preservados</t>
+          <t>roteamento_fracao_transmissao</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
@@ -44383,14 +45348,14 @@
         </is>
       </c>
       <c r="C178" s="2" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>8.173395242890144e-17</v>
       </c>
       <c r="D178" s="2" t="n">
-        <v>1e-06</v>
+        <v>1e-09</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>os fluxos alvo→alvo entre as regiões (ex.: RS→RS, RS→RB, RB→RS, RB→RB) são os da original</t>
+          <t>fração da transmissão paga pela distribuição e pela geração das regiões desagregadas (o S38 agregado de região não desagregada recebe a sua parte inteira)</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -44402,7 +45367,7 @@
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>subsetores_latentes</t>
+          <t>bloco_fluxos_regionais_preservados</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -44411,14 +45376,14 @@
         </is>
       </c>
       <c r="C179" s="2" t="n">
-        <v>2</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="D179" s="2" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>colunas de coeficientes guardadas à parte: RS_S38_SOL, RS_S38_PET</t>
+          <t>os fluxos alvo→alvo entre as regiões (ex.: RS→RS, RS→RB, RB→RS, RB→RB) são os da original</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -44430,7 +45395,7 @@
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>piso_vbp_combustivel</t>
+          <t>subsetores_latentes</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
@@ -44439,14 +45404,14 @@
         </is>
       </c>
       <c r="C180" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D180" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>VBP ≥ combustível ÷ κ (κ = 0.7); RS_S38_BIO: combustível/VBP = 0.0248; RS_S38_CAR: combustível/VBP = 0.0212; RS_S38_GN: combustível/VBP = 0.7000; RB_S38_BIO: combustível/VBP = 0.0198; RB_S38_CAR: combustível/VBP = 0.1044; RB_S38_GN: combustível/VBP = 0.7000; RB_S38_PET: combustível/VBP = 0.7000</t>
+          <t>colunas de coeficientes guardadas à parte: RS_S38_SOL, RS_S38_PET</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -44458,7 +45423,7 @@
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>EOB_minimo_eta</t>
+          <t>piso_vbp_combustivel</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
@@ -44467,14 +45432,14 @@
         </is>
       </c>
       <c r="C181" s="2" t="n">
-        <v>0.09999999999999999</v>
+        <v>0</v>
       </c>
       <c r="D181" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>EOB ≥ η × VBP (η = 0.1; tolerância absoluta 1e-06 R$ mi) em todo subsetor com produção</t>
+          <t>VBP ≥ combustível ÷ κ (κ = 0.7); RS_S38_BIO: combustível/VBP = 0.0248; RS_S38_CAR: combustível/VBP = 0.0212; RS_S38_GN: combustível/VBP = 0.7000; RB_S38_BIO: combustível/VBP = 0.0198; RB_S38_CAR: combustível/VBP = 0.1044; RB_S38_GN: combustível/VBP = 0.7000; RB_S38_PET: combustível/VBP = 0.7000</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -44486,7 +45451,7 @@
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>reequilibrio_insumos_fixos</t>
+          <t>EOB_minimo_eta</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
@@ -44495,14 +45460,14 @@
         </is>
       </c>
       <c r="C182" s="2" t="n">
-        <v>0</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="D182" s="2" t="n">
-        <v>1e-06</v>
+        <v>0.1</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>bloco, combustíveis, importações, remunerações e impostos sobre a produção iguais antes e depois do reequilíbrio</t>
+          <t>EOB ≥ η × VBP (η = 0.1; tolerância absoluta 1e-06 R$ mi) em todo subsetor com produção</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -44514,7 +45479,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>reequilibrio_soma_EOB_regiao</t>
+          <t>reequilibrio_insumos_fixos</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -44523,14 +45488,14 @@
         </is>
       </c>
       <c r="C183" s="2" t="n">
-        <v>2.91038304567337e-11</v>
+        <v>0</v>
       </c>
       <c r="D183" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>Σ EOB dos subsetores de cada região = EOB original do setor-alvo; RB: Σ EOB = 103643.5529; RS: Σ EOB = 6737.4468</t>
+          <t>bloco, combustíveis, importações, remunerações e impostos sobre a produção iguais antes e depois do reequilíbrio</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
@@ -44542,23 +45507,23 @@
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>insumos_nao_energeticos_minimo</t>
+          <t>reequilibrio_soma_EOB_regiao</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>ALERTA</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="C184" s="2" t="n">
-        <v>0.02567660099411299</v>
+        <v>2.91038304567337e-11</v>
       </c>
       <c r="D184" s="2" t="n">
-        <v>0.05</v>
+        <v>1e-06</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>compras a setores fora do bloco, exceto combustíveis, ÷ VBP ≥ 0.05 em todo subsetor com produção: abaixo em RS_S38_GN (0.0257), RB_S38_GN (0.0315)</t>
+          <t>Σ EOB dos subsetores de cada região = EOB original do setor-alvo; RB: Σ EOB = 103643.5529; RS: Σ EOB = 6737.4468</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
@@ -44570,7 +45535,7 @@
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>multiplicador_producao_subsetores</t>
+          <t>insumos_nao_energeticos_minimo</t>
         </is>
       </c>
       <c r="B185" t="inlineStr">
@@ -44579,14 +45544,14 @@
         </is>
       </c>
       <c r="C185" s="2" t="n">
-        <v>2.801481802009222</v>
+        <v>0.02567660099411299</v>
       </c>
       <c r="D185" s="2" t="n">
-        <v>2.2</v>
+        <v>0.05</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
-          <t>multiplicador de produção (Σ coluna de L, inclui latentes) ≤ 2.2: acima em RS_S38_GN (2.397), RS_S38_PET (2.801), RS_S38_GAS (2.344), RB_S38_PET (2.760)</t>
+          <t>compras a setores fora do bloco, exceto combustíveis, ÷ VBP ≥ 0.05 em todo subsetor com produção: abaixo em RS_S38_GN (0.0257), RB_S38_GN (0.0315)</t>
         </is>
       </c>
       <c r="F185" t="inlineStr">
@@ -44598,35 +45563,35 @@
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>reagregacao_Z</t>
+          <t>multiplicador_producao_subsetores</t>
         </is>
       </c>
       <c r="B186" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>ALERTA</t>
         </is>
       </c>
       <c r="C186" s="2" t="n">
-        <v>2.582964953035116e-10</v>
+        <v>2.801481802009222</v>
       </c>
       <c r="D186" s="2" t="n">
-        <v>1e-06</v>
+        <v>2.2</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
-          <t>máx |Σ subsetores − original|</t>
+          <t>multiplicador de produção (Σ coluna de L, inclui latentes) ≤ 2.2: acima em RS_S38_GN (2.397), RS_S38_PET (2.801), RS_S38_GAS (2.344), RB_S38_PET (2.760)</t>
         </is>
       </c>
       <c r="F186" t="inlineStr">
         <is>
-          <t>v04_gas4dist</t>
+          <t>v04_E4</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>reagregacao_F</t>
+          <t>reagregacao_Z</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
@@ -44635,7 +45600,7 @@
         </is>
       </c>
       <c r="C187" s="2" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>2.582964953035116e-10</v>
       </c>
       <c r="D187" s="2" t="n">
         <v>1e-06</v>
@@ -44654,7 +45619,7 @@
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>reagregacao_X</t>
+          <t>reagregacao_F</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
@@ -44663,7 +45628,7 @@
         </is>
       </c>
       <c r="C188" s="2" t="n">
-        <v>3.637978807091713e-12</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="D188" s="2" t="n">
         <v>1e-06</v>
@@ -44682,7 +45647,7 @@
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>reagregacao_total_linha</t>
+          <t>reagregacao_X</t>
         </is>
       </c>
       <c r="B189" t="inlineStr">
@@ -44710,7 +45675,7 @@
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>reagregacao_V</t>
+          <t>reagregacao_total_linha</t>
         </is>
       </c>
       <c r="B190" t="inlineStr">
@@ -44719,7 +45684,7 @@
         </is>
       </c>
       <c r="C190" s="2" t="n">
-        <v>1.425632945029065e-09</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="D190" s="2" t="n">
         <v>1e-06</v>
@@ -44738,7 +45703,7 @@
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>reagregacao_S</t>
+          <t>reagregacao_V</t>
         </is>
       </c>
       <c r="B191" t="inlineStr">
@@ -44747,7 +45712,7 @@
         </is>
       </c>
       <c r="C191" s="2" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>1.425632945029065e-09</v>
       </c>
       <c r="D191" s="2" t="n">
         <v>1e-06</v>
@@ -44766,7 +45731,7 @@
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>reagregacao_V_df</t>
+          <t>reagregacao_S</t>
         </is>
       </c>
       <c r="B192" t="inlineStr">
@@ -44775,7 +45740,7 @@
         </is>
       </c>
       <c r="C192" s="2" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="D192" s="2" t="n">
         <v>1e-06</v>
@@ -44794,7 +45759,7 @@
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>reagregacao_X_df</t>
+          <t>reagregacao_V_df</t>
         </is>
       </c>
       <c r="B193" t="inlineStr">
@@ -44822,7 +45787,7 @@
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>reagregacao_totais_EV</t>
+          <t>reagregacao_X_df</t>
         </is>
       </c>
       <c r="B194" t="inlineStr">
@@ -44836,7 +45801,11 @@
       <c r="D194" s="2" t="n">
         <v>1e-06</v>
       </c>
-      <c r="E194" t="inlineStr"/>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>máx |Σ subsetores − original|</t>
+        </is>
+      </c>
       <c r="F194" t="inlineStr">
         <is>
           <t>v04_gas4dist</t>
@@ -44846,7 +45815,7 @@
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>balanco_linha_subsetores</t>
+          <t>reagregacao_totais_EV</t>
         </is>
       </c>
       <c r="B195" t="inlineStr">
@@ -44855,16 +45824,12 @@
         </is>
       </c>
       <c r="C195" s="2" t="n">
-        <v>7.428752724081278e-09</v>
+        <v>0</v>
       </c>
       <c r="D195" s="2" t="n">
         <v>1e-06</v>
       </c>
-      <c r="E195" t="inlineStr">
-        <is>
-          <t>máx |Σ vendas − VBP| nos subsetores (tolerância + resíduo original × participação)</t>
-        </is>
-      </c>
+      <c r="E195" t="inlineStr"/>
       <c r="F195" t="inlineStr">
         <is>
           <t>v04_gas4dist</t>
@@ -44874,7 +45839,7 @@
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>balanco_coluna_subsetores</t>
+          <t>balanco_linha_subsetores</t>
         </is>
       </c>
       <c r="B196" t="inlineStr">
@@ -44883,14 +45848,14 @@
         </is>
       </c>
       <c r="C196" s="2" t="n">
-        <v>6.543927162303009e-11</v>
+        <v>7.428752724081278e-09</v>
       </c>
       <c r="D196" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
-          <t>máx |resíduo da coluna − participação × resíduo original| (o resíduo original é repartido pelo VBP)</t>
+          <t>máx |Σ vendas − VBP| nos subsetores (tolerância + resíduo original × participação)</t>
         </is>
       </c>
       <c r="F196" t="inlineStr">
@@ -44902,7 +45867,7 @@
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>identidade_VA_subsetores</t>
+          <t>balanco_coluna_subsetores</t>
         </is>
       </c>
       <c r="B197" t="inlineStr">
@@ -44911,14 +45876,14 @@
         </is>
       </c>
       <c r="C197" s="2" t="n">
-        <v>6.366462912410498e-12</v>
+        <v>6.543927162303009e-11</v>
       </c>
       <c r="D197" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
-          <t>VA − (remunerações + EOB + impostos sobre a produção)</t>
+          <t>máx |resíduo da coluna − participação × resíduo original| (o resíduo original é repartido pelo VBP)</t>
         </is>
       </c>
       <c r="F197" t="inlineStr">
@@ -44930,7 +45895,7 @@
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>nao_negatividade</t>
+          <t>identidade_VA_subsetores</t>
         </is>
       </c>
       <c r="B198" t="inlineStr">
@@ -44939,14 +45904,14 @@
         </is>
       </c>
       <c r="C198" s="2" t="n">
-        <v>0</v>
+        <v>6.366462912410498e-12</v>
       </c>
       <c r="D198" s="2" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
-          <t>negativos só onde a original já tem (coluna de discrepância, EOB, impostos sobre a produção); nenhum negativo novo</t>
+          <t>VA − (remunerações + EOB + impostos sobre a produção)</t>
         </is>
       </c>
       <c r="F198" t="inlineStr">
@@ -44958,7 +45923,7 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>satelite_ocupacoes_preservado</t>
+          <t>nao_negatividade</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
@@ -44967,12 +45932,16 @@
         </is>
       </c>
       <c r="C199" s="2" t="n">
-        <v>3.637978807091713e-12</v>
+        <v>0</v>
       </c>
       <c r="D199" s="2" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="E199" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>negativos só onde a original já tem (coluna de discrepância, EOB, impostos sobre a produção); nenhum negativo novo</t>
+        </is>
+      </c>
       <c r="F199" t="inlineStr">
         <is>
           <t>v04_gas4dist</t>
@@ -44982,7 +45951,7 @@
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>satelite_co2e_preservado</t>
+          <t>satelite_ocupacoes_preservado</t>
         </is>
       </c>
       <c r="B200" t="inlineStr">
@@ -44991,7 +45960,7 @@
         </is>
       </c>
       <c r="C200" s="2" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="D200" s="2" t="n">
         <v>1e-06</v>
@@ -45006,7 +45975,7 @@
     <row r="201">
       <c r="A201" t="inlineStr">
         <is>
-          <t>satelite_agua_preservado</t>
+          <t>satelite_co2e_preservado</t>
         </is>
       </c>
       <c r="B201" t="inlineStr">
@@ -45015,7 +45984,7 @@
         </is>
       </c>
       <c r="C201" s="2" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>0</v>
       </c>
       <c r="D201" s="2" t="n">
         <v>1e-06</v>
@@ -45030,7 +45999,7 @@
     <row r="202">
       <c r="A202" t="inlineStr">
         <is>
-          <t>satelite_energia_preservado</t>
+          <t>satelite_agua_preservado</t>
         </is>
       </c>
       <c r="B202" t="inlineStr">
@@ -45039,7 +46008,7 @@
         </is>
       </c>
       <c r="C202" s="2" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="D202" s="2" t="n">
         <v>1e-06</v>
@@ -45054,7 +46023,7 @@
     <row r="203">
       <c r="A203" t="inlineStr">
         <is>
-          <t>niveis_residuo_nao_negativo</t>
+          <t>satelite_energia_preservado</t>
         </is>
       </c>
       <c r="B203" t="inlineStr">
@@ -45063,16 +46032,12 @@
         </is>
       </c>
       <c r="C203" s="2" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="D203" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E203" t="inlineStr">
-        <is>
-          <t>RS co2e (residuo): identificado 3862147.8290, resíduo 1975857.7254; RB co2e (residuo): identificado 34828615.1621, resíduo 49689733.8945</t>
-        </is>
-      </c>
+        <v>1e-06</v>
+      </c>
+      <c r="E203" t="inlineStr"/>
       <c r="F203" t="inlineStr">
         <is>
           <t>v04_gas4dist</t>
@@ -45082,7 +46047,7 @@
     <row r="204">
       <c r="A204" t="inlineStr">
         <is>
-          <t>EOB_nao_negativo_subsetores</t>
+          <t>niveis_residuo_nao_negativo</t>
         </is>
       </c>
       <c r="B204" t="inlineStr">
@@ -45098,7 +46063,7 @@
       </c>
       <c r="E204" t="inlineStr">
         <is>
-          <t>todos ≥ 0</t>
+          <t>RS co2e (residuo): identificado 3862147.8290, resíduo 1975857.7254; RB co2e (residuo): identificado 34828615.1621, resíduo 49689733.8945</t>
         </is>
       </c>
       <c r="F204" t="inlineStr">
@@ -45110,7 +46075,7 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>subsetores_producao_zero_zerados</t>
+          <t>EOB_nao_negativo_subsetores</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
@@ -45119,14 +46084,14 @@
         </is>
       </c>
       <c r="C205" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D205" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
-          <t>3 subsetor(es) com produção zero: RS_S38_SOL, RS_S38_PET, RS_S38_NUC</t>
+          <t>todos ≥ 0</t>
         </is>
       </c>
       <c r="F205" t="inlineStr">
@@ -45138,7 +46103,7 @@
     <row r="206">
       <c r="A206" t="inlineStr">
         <is>
-          <t>L_nao_negativa</t>
+          <t>subsetores_producao_zero_zerados</t>
         </is>
       </c>
       <c r="B206" t="inlineStr">
@@ -45147,12 +46112,16 @@
         </is>
       </c>
       <c r="C206" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D206" s="2" t="n">
-        <v>-1e-10</v>
-      </c>
-      <c r="E206" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>3 subsetor(es) com produção zero: RS_S38_SOL, RS_S38_PET, RS_S38_NUC</t>
+        </is>
+      </c>
       <c r="F206" t="inlineStr">
         <is>
           <t>v04_gas4dist</t>
@@ -45162,7 +46131,7 @@
     <row r="207">
       <c r="A207" t="inlineStr">
         <is>
-          <t>L_diagonal_maior_igual_1</t>
+          <t>L_nao_negativa</t>
         </is>
       </c>
       <c r="B207" t="inlineStr">
@@ -45171,10 +46140,10 @@
         </is>
       </c>
       <c r="C207" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D207" s="2" t="n">
-        <v>1</v>
+        <v>-1e-10</v>
       </c>
       <c r="E207" t="inlineStr"/>
       <c r="F207" t="inlineStr">
@@ -45186,7 +46155,7 @@
     <row r="208">
       <c r="A208" t="inlineStr">
         <is>
-          <t>A_soma_colunas_menor_1</t>
+          <t>L_diagonal_maior_igual_1</t>
         </is>
       </c>
       <c r="B208" t="inlineStr">
@@ -45195,16 +46164,12 @@
         </is>
       </c>
       <c r="C208" s="2" t="n">
-        <v>0.8501168940529817</v>
+        <v>1</v>
       </c>
       <c r="D208" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E208" t="inlineStr">
-        <is>
-          <t>Σ coeficientes técnicos de cada coluna (inclui latentes)</t>
-        </is>
-      </c>
+      <c r="E208" t="inlineStr"/>
       <c r="F208" t="inlineStr">
         <is>
           <t>v04_gas4dist</t>
@@ -45214,7 +46179,7 @@
     <row r="209">
       <c r="A209" t="inlineStr">
         <is>
-          <t>RAS_convergencia</t>
+          <t>A_soma_colunas_menor_1</t>
         </is>
       </c>
       <c r="B209" t="inlineStr">
@@ -45223,14 +46188,14 @@
         </is>
       </c>
       <c r="C209" s="2" t="n">
-        <v>28</v>
+        <v>0.8501168940529817</v>
       </c>
       <c r="D209" s="2" t="n">
-        <v>20000</v>
+        <v>1</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
-          <t>linhas RS S38: necessário, convergiu em 22 iterações, erro 4.98e-09 (inicial 4.21e-01); linhas RB S38: necessário, convergiu em 28 iterações, erro 7.43e-09 (inicial 1.91e+00); reequilibrio_EOB RS (η = 0.1): necessário, convergiu em 7 iterações, erro 1.43e-09 (inicial 1.26e+02); reequilibrio_EOB RB (η = 0.1): necessário, convergiu em 8 iterações, erro 1.18e-09 (inicial 2.46e+03)</t>
+          <t>Σ coeficientes técnicos de cada coluna (inclui latentes)</t>
         </is>
       </c>
       <c r="F209" t="inlineStr">
@@ -45242,7 +46207,7 @@
     <row r="210">
       <c r="A210" t="inlineStr">
         <is>
-          <t>roteamento_vendas_geracao_igual_E</t>
+          <t>RAS_convergencia</t>
         </is>
       </c>
       <c r="B210" t="inlineStr">
@@ -45251,14 +46216,14 @@
         </is>
       </c>
       <c r="C210" s="2" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>28</v>
       </c>
       <c r="D210" s="2" t="n">
-        <v>1e-06</v>
+        <v>20000</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
-          <t>Σ vendas da geração de r dentro do bloco = E_r = F_r − T_r − G_r</t>
+          <t>linhas RS S38: necessário, convergiu em 22 iterações, erro 4.98e-09 (inicial 4.21e-01); linhas RB S38: necessário, convergiu em 28 iterações, erro 7.43e-09 (inicial 1.91e+00); reequilibrio_EOB RS (η = 0.1): necessário, convergiu em 7 iterações, erro 1.43e-09 (inicial 1.26e+02); reequilibrio_EOB RB (η = 0.1): necessário, convergiu em 8 iterações, erro 1.18e-09 (inicial 2.46e+03)</t>
         </is>
       </c>
       <c r="F210" t="inlineStr">
@@ -45270,7 +46235,7 @@
     <row r="211">
       <c r="A211" t="inlineStr">
         <is>
-          <t>roteamento_vendas_transmissao_igual_T</t>
+          <t>roteamento_vendas_geracao_igual_E</t>
         </is>
       </c>
       <c r="B211" t="inlineStr">
@@ -45279,14 +46244,14 @@
         </is>
       </c>
       <c r="C211" s="2" t="n">
-        <v>0</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="D211" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
-          <t>Σ vendas da transmissão de r dentro do bloco = T_r</t>
+          <t>Σ vendas da geração de r dentro do bloco = E_r = F_r − T_r − G_r</t>
         </is>
       </c>
       <c r="F211" t="inlineStr">
@@ -45298,7 +46263,7 @@
     <row r="212">
       <c r="A212" t="inlineStr">
         <is>
-          <t>roteamento_geracao_e_transmissao_nao_vendem_fora</t>
+          <t>roteamento_vendas_transmissao_igual_T</t>
         </is>
       </c>
       <c r="B212" t="inlineStr">
@@ -45314,7 +46279,7 @@
       </c>
       <c r="E212" t="inlineStr">
         <is>
-          <t>Σ |vendas| da geração e da transmissão fora do bloco e à demanda final (Seção 6.4)</t>
+          <t>Σ vendas da transmissão de r dentro do bloco = T_r</t>
         </is>
       </c>
       <c r="F212" t="inlineStr">
@@ -45326,7 +46291,7 @@
     <row r="213">
       <c r="A213" t="inlineStr">
         <is>
-          <t>roteamento_fracao_transmissao</t>
+          <t>roteamento_geracao_e_transmissao_nao_vendem_fora</t>
         </is>
       </c>
       <c r="B213" t="inlineStr">
@@ -45335,14 +46300,14 @@
         </is>
       </c>
       <c r="C213" s="2" t="n">
-        <v>8.173395242890144e-17</v>
+        <v>0</v>
       </c>
       <c r="D213" s="2" t="n">
-        <v>1e-09</v>
+        <v>1e-06</v>
       </c>
       <c r="E213" t="inlineStr">
         <is>
-          <t>fração da transmissão paga pela distribuição e pela geração das regiões desagregadas (o S38 agregado de região não desagregada recebe a sua parte inteira)</t>
+          <t>Σ |vendas| da geração e da transmissão fora do bloco e à demanda final (Seção 6.4)</t>
         </is>
       </c>
       <c r="F213" t="inlineStr">
@@ -45354,7 +46319,7 @@
     <row r="214">
       <c r="A214" t="inlineStr">
         <is>
-          <t>bloco_fluxos_regionais_preservados</t>
+          <t>roteamento_fracao_transmissao</t>
         </is>
       </c>
       <c r="B214" t="inlineStr">
@@ -45363,14 +46328,14 @@
         </is>
       </c>
       <c r="C214" s="2" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>8.173395242890144e-17</v>
       </c>
       <c r="D214" s="2" t="n">
-        <v>1e-06</v>
+        <v>1e-09</v>
       </c>
       <c r="E214" t="inlineStr">
         <is>
-          <t>os fluxos alvo→alvo entre as regiões (ex.: RS→RS, RS→RB, RB→RS, RB→RB) são os da original</t>
+          <t>fração da transmissão paga pela distribuição e pela geração das regiões desagregadas (o S38 agregado de região não desagregada recebe a sua parte inteira)</t>
         </is>
       </c>
       <c r="F214" t="inlineStr">
@@ -45382,7 +46347,7 @@
     <row r="215">
       <c r="A215" t="inlineStr">
         <is>
-          <t>subsetores_latentes</t>
+          <t>bloco_fluxos_regionais_preservados</t>
         </is>
       </c>
       <c r="B215" t="inlineStr">
@@ -45391,14 +46356,14 @@
         </is>
       </c>
       <c r="C215" s="2" t="n">
-        <v>2</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="D215" s="2" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="E215" t="inlineStr">
         <is>
-          <t>colunas de coeficientes guardadas à parte: RS_S38_SOL, RS_S38_PET</t>
+          <t>os fluxos alvo→alvo entre as regiões (ex.: RS→RS, RS→RB, RB→RS, RB→RB) são os da original</t>
         </is>
       </c>
       <c r="F215" t="inlineStr">
@@ -45410,7 +46375,7 @@
     <row r="216">
       <c r="A216" t="inlineStr">
         <is>
-          <t>piso_vbp_combustivel</t>
+          <t>subsetores_latentes</t>
         </is>
       </c>
       <c r="B216" t="inlineStr">
@@ -45419,14 +46384,14 @@
         </is>
       </c>
       <c r="C216" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D216" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E216" t="inlineStr">
         <is>
-          <t>VBP ≥ combustível ÷ κ (κ = 0.7); RS_S38_BIO: combustível/VBP = 0.0248; RS_S38_CAR: combustível/VBP = 0.0212; RS_S38_GN: combustível/VBP = 0.7000; RB_S38_BIO: combustível/VBP = 0.0198; RB_S38_CAR: combustível/VBP = 0.1044; RB_S38_GN: combustível/VBP = 0.7000; RB_S38_PET: combustível/VBP = 0.7000</t>
+          <t>colunas de coeficientes guardadas à parte: RS_S38_SOL, RS_S38_PET</t>
         </is>
       </c>
       <c r="F216" t="inlineStr">
@@ -45438,7 +46403,7 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>EOB_minimo_eta</t>
+          <t>piso_vbp_combustivel</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
@@ -45447,14 +46412,14 @@
         </is>
       </c>
       <c r="C217" s="2" t="n">
-        <v>0.09999999999999999</v>
+        <v>0</v>
       </c>
       <c r="D217" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E217" t="inlineStr">
         <is>
-          <t>EOB ≥ η × VBP (η = 0.1; tolerância absoluta 1e-06 R$ mi) em todo subsetor com produção</t>
+          <t>VBP ≥ combustível ÷ κ (κ = 0.7); RS_S38_BIO: combustível/VBP = 0.0248; RS_S38_CAR: combustível/VBP = 0.0212; RS_S38_GN: combustível/VBP = 0.7000; RB_S38_BIO: combustível/VBP = 0.0198; RB_S38_CAR: combustível/VBP = 0.1044; RB_S38_GN: combustível/VBP = 0.7000; RB_S38_PET: combustível/VBP = 0.7000</t>
         </is>
       </c>
       <c r="F217" t="inlineStr">
@@ -45466,7 +46431,7 @@
     <row r="218">
       <c r="A218" t="inlineStr">
         <is>
-          <t>reequilibrio_insumos_fixos</t>
+          <t>EOB_minimo_eta</t>
         </is>
       </c>
       <c r="B218" t="inlineStr">
@@ -45475,14 +46440,14 @@
         </is>
       </c>
       <c r="C218" s="2" t="n">
-        <v>0</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="D218" s="2" t="n">
-        <v>1e-06</v>
+        <v>0.1</v>
       </c>
       <c r="E218" t="inlineStr">
         <is>
-          <t>bloco, combustíveis, importações, remunerações e impostos sobre a produção iguais antes e depois do reequilíbrio</t>
+          <t>EOB ≥ η × VBP (η = 0.1; tolerância absoluta 1e-06 R$ mi) em todo subsetor com produção</t>
         </is>
       </c>
       <c r="F218" t="inlineStr">
@@ -45494,7 +46459,7 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>reequilibrio_soma_EOB_regiao</t>
+          <t>reequilibrio_insumos_fixos</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
@@ -45503,14 +46468,14 @@
         </is>
       </c>
       <c r="C219" s="2" t="n">
-        <v>5.820766091346741e-11</v>
+        <v>0</v>
       </c>
       <c r="D219" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E219" t="inlineStr">
         <is>
-          <t>Σ EOB dos subsetores de cada região = EOB original do setor-alvo; RB: Σ EOB = 103643.5529; RS: Σ EOB = 6737.4468</t>
+          <t>bloco, combustíveis, importações, remunerações e impostos sobre a produção iguais antes e depois do reequilíbrio</t>
         </is>
       </c>
       <c r="F219" t="inlineStr">
@@ -45522,23 +46487,23 @@
     <row r="220">
       <c r="A220" t="inlineStr">
         <is>
-          <t>insumos_nao_energeticos_minimo</t>
+          <t>reequilibrio_soma_EOB_regiao</t>
         </is>
       </c>
       <c r="B220" t="inlineStr">
         <is>
-          <t>ALERTA</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="C220" s="2" t="n">
-        <v>0.02567660099411299</v>
+        <v>5.820766091346741e-11</v>
       </c>
       <c r="D220" s="2" t="n">
-        <v>0.05</v>
+        <v>1e-06</v>
       </c>
       <c r="E220" t="inlineStr">
         <is>
-          <t>compras a setores fora do bloco, exceto combustíveis, ÷ VBP ≥ 0.05 em todo subsetor com produção: abaixo em RS_S38_GN (0.0257), RB_S38_GN (0.0315)</t>
+          <t>Σ EOB dos subsetores de cada região = EOB original do setor-alvo; RB: Σ EOB = 103643.5529; RS: Σ EOB = 6737.4468</t>
         </is>
       </c>
       <c r="F220" t="inlineStr">
@@ -45550,7 +46515,7 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>multiplicador_producao_subsetores</t>
+          <t>insumos_nao_energeticos_minimo</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
@@ -45559,14 +46524,14 @@
         </is>
       </c>
       <c r="C221" s="2" t="n">
-        <v>2.801398931781818</v>
+        <v>0.02567660099411299</v>
       </c>
       <c r="D221" s="2" t="n">
-        <v>2.2</v>
+        <v>0.05</v>
       </c>
       <c r="E221" t="inlineStr">
         <is>
-          <t>multiplicador de produção (Σ coluna de L, inclui latentes) ≤ 2.2: acima em RS_S38_GN (2.397), RS_S38_PET (2.801), RS_S38_GAS (2.344), RB_S38_PET (2.760)</t>
+          <t>compras a setores fora do bloco, exceto combustíveis, ÷ VBP ≥ 0.05 em todo subsetor com produção: abaixo em RS_S38_GN (0.0257), RB_S38_GN (0.0315)</t>
         </is>
       </c>
       <c r="F221" t="inlineStr">
@@ -45578,35 +46543,35 @@
     <row r="222">
       <c r="A222" t="inlineStr">
         <is>
-          <t>reagregacao_Z</t>
+          <t>multiplicador_producao_subsetores</t>
         </is>
       </c>
       <c r="B222" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>ALERTA</t>
         </is>
       </c>
       <c r="C222" s="2" t="n">
-        <v>1.909938873723149e-10</v>
+        <v>2.801398931781818</v>
       </c>
       <c r="D222" s="2" t="n">
-        <v>1e-06</v>
+        <v>2.2</v>
       </c>
       <c r="E222" t="inlineStr">
         <is>
-          <t>máx |Σ subsetores − original|</t>
+          <t>multiplicador de produção (Σ coluna de L, inclui latentes) ≤ 2.2: acima em RS_S38_GN (2.397), RS_S38_PET (2.801), RS_S38_GAS (2.344), RB_S38_PET (2.760)</t>
         </is>
       </c>
       <c r="F222" t="inlineStr">
         <is>
-          <t>v04_rap_media</t>
+          <t>v04_gas4dist</t>
         </is>
       </c>
     </row>
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>reagregacao_F</t>
+          <t>reagregacao_Z</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
@@ -45615,7 +46580,7 @@
         </is>
       </c>
       <c r="C223" s="2" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>1.909938873723149e-10</v>
       </c>
       <c r="D223" s="2" t="n">
         <v>1e-06</v>
@@ -45634,7 +46599,7 @@
     <row r="224">
       <c r="A224" t="inlineStr">
         <is>
-          <t>reagregacao_X</t>
+          <t>reagregacao_F</t>
         </is>
       </c>
       <c r="B224" t="inlineStr">
@@ -45643,7 +46608,7 @@
         </is>
       </c>
       <c r="C224" s="2" t="n">
-        <v>5.820766091346741e-11</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="D224" s="2" t="n">
         <v>1e-06</v>
@@ -45662,7 +46627,7 @@
     <row r="225">
       <c r="A225" t="inlineStr">
         <is>
-          <t>reagregacao_total_linha</t>
+          <t>reagregacao_X</t>
         </is>
       </c>
       <c r="B225" t="inlineStr">
@@ -45690,7 +46655,7 @@
     <row r="226">
       <c r="A226" t="inlineStr">
         <is>
-          <t>reagregacao_V</t>
+          <t>reagregacao_total_linha</t>
         </is>
       </c>
       <c r="B226" t="inlineStr">
@@ -45699,7 +46664,7 @@
         </is>
       </c>
       <c r="C226" s="2" t="n">
-        <v>1.028865881380625e-09</v>
+        <v>5.820766091346741e-11</v>
       </c>
       <c r="D226" s="2" t="n">
         <v>1e-06</v>
@@ -45718,7 +46683,7 @@
     <row r="227">
       <c r="A227" t="inlineStr">
         <is>
-          <t>reagregacao_S</t>
+          <t>reagregacao_V</t>
         </is>
       </c>
       <c r="B227" t="inlineStr">
@@ -45727,7 +46692,7 @@
         </is>
       </c>
       <c r="C227" s="2" t="n">
-        <v>2.91038304567337e-11</v>
+        <v>1.028865881380625e-09</v>
       </c>
       <c r="D227" s="2" t="n">
         <v>1e-06</v>
@@ -45746,7 +46711,7 @@
     <row r="228">
       <c r="A228" t="inlineStr">
         <is>
-          <t>reagregacao_V_df</t>
+          <t>reagregacao_S</t>
         </is>
       </c>
       <c r="B228" t="inlineStr">
@@ -45755,7 +46720,7 @@
         </is>
       </c>
       <c r="C228" s="2" t="n">
-        <v>0</v>
+        <v>2.91038304567337e-11</v>
       </c>
       <c r="D228" s="2" t="n">
         <v>1e-06</v>
@@ -45774,7 +46739,7 @@
     <row r="229">
       <c r="A229" t="inlineStr">
         <is>
-          <t>reagregacao_X_df</t>
+          <t>reagregacao_V_df</t>
         </is>
       </c>
       <c r="B229" t="inlineStr">
@@ -45802,7 +46767,7 @@
     <row r="230">
       <c r="A230" t="inlineStr">
         <is>
-          <t>reagregacao_totais_EV</t>
+          <t>reagregacao_X_df</t>
         </is>
       </c>
       <c r="B230" t="inlineStr">
@@ -45816,7 +46781,11 @@
       <c r="D230" s="2" t="n">
         <v>1e-06</v>
       </c>
-      <c r="E230" t="inlineStr"/>
+      <c r="E230" t="inlineStr">
+        <is>
+          <t>máx |Σ subsetores − original|</t>
+        </is>
+      </c>
       <c r="F230" t="inlineStr">
         <is>
           <t>v04_rap_media</t>
@@ -45826,7 +46795,7 @@
     <row r="231">
       <c r="A231" t="inlineStr">
         <is>
-          <t>balanco_linha_subsetores</t>
+          <t>reagregacao_totais_EV</t>
         </is>
       </c>
       <c r="B231" t="inlineStr">
@@ -45835,16 +46804,12 @@
         </is>
       </c>
       <c r="C231" s="2" t="n">
-        <v>8.552888175472617e-09</v>
+        <v>0</v>
       </c>
       <c r="D231" s="2" t="n">
         <v>1e-06</v>
       </c>
-      <c r="E231" t="inlineStr">
-        <is>
-          <t>máx |Σ vendas − VBP| nos subsetores (tolerância + resíduo original × participação)</t>
-        </is>
-      </c>
+      <c r="E231" t="inlineStr"/>
       <c r="F231" t="inlineStr">
         <is>
           <t>v04_rap_media</t>
@@ -45854,7 +46819,7 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>balanco_coluna_subsetores</t>
+          <t>balanco_linha_subsetores</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
@@ -45863,14 +46828,14 @@
         </is>
       </c>
       <c r="C232" s="2" t="n">
-        <v>7.441114282906447e-11</v>
+        <v>8.552888175472617e-09</v>
       </c>
       <c r="D232" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E232" t="inlineStr">
         <is>
-          <t>máx |resíduo da coluna − participação × resíduo original| (o resíduo original é repartido pelo VBP)</t>
+          <t>máx |Σ vendas − VBP| nos subsetores (tolerância + resíduo original × participação)</t>
         </is>
       </c>
       <c r="F232" t="inlineStr">
@@ -45882,7 +46847,7 @@
     <row r="233">
       <c r="A233" t="inlineStr">
         <is>
-          <t>identidade_VA_subsetores</t>
+          <t>balanco_coluna_subsetores</t>
         </is>
       </c>
       <c r="B233" t="inlineStr">
@@ -45891,14 +46856,14 @@
         </is>
       </c>
       <c r="C233" s="2" t="n">
-        <v>1.364242052659392e-11</v>
+        <v>7.441114282906447e-11</v>
       </c>
       <c r="D233" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E233" t="inlineStr">
         <is>
-          <t>VA − (remunerações + EOB + impostos sobre a produção)</t>
+          <t>máx |resíduo da coluna − participação × resíduo original| (o resíduo original é repartido pelo VBP)</t>
         </is>
       </c>
       <c r="F233" t="inlineStr">
@@ -45910,7 +46875,7 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>nao_negatividade</t>
+          <t>identidade_VA_subsetores</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
@@ -45919,14 +46884,14 @@
         </is>
       </c>
       <c r="C234" s="2" t="n">
-        <v>0</v>
+        <v>1.364242052659392e-11</v>
       </c>
       <c r="D234" s="2" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="E234" t="inlineStr">
         <is>
-          <t>negativos só onde a original já tem (coluna de discrepância, EOB, impostos sobre a produção); nenhum negativo novo</t>
+          <t>VA − (remunerações + EOB + impostos sobre a produção)</t>
         </is>
       </c>
       <c r="F234" t="inlineStr">
@@ -45938,7 +46903,7 @@
     <row r="235">
       <c r="A235" t="inlineStr">
         <is>
-          <t>satelite_ocupacoes_preservado</t>
+          <t>nao_negatividade</t>
         </is>
       </c>
       <c r="B235" t="inlineStr">
@@ -45947,12 +46912,16 @@
         </is>
       </c>
       <c r="C235" s="2" t="n">
-        <v>3.637978807091713e-12</v>
+        <v>0</v>
       </c>
       <c r="D235" s="2" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="E235" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E235" t="inlineStr">
+        <is>
+          <t>negativos só onde a original já tem (coluna de discrepância, EOB, impostos sobre a produção); nenhum negativo novo</t>
+        </is>
+      </c>
       <c r="F235" t="inlineStr">
         <is>
           <t>v04_rap_media</t>
@@ -45962,7 +46931,7 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>satelite_co2e_preservado</t>
+          <t>satelite_ocupacoes_preservado</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
@@ -45971,7 +46940,7 @@
         </is>
       </c>
       <c r="C236" s="2" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="D236" s="2" t="n">
         <v>1e-06</v>
@@ -45986,7 +46955,7 @@
     <row r="237">
       <c r="A237" t="inlineStr">
         <is>
-          <t>satelite_agua_preservado</t>
+          <t>satelite_co2e_preservado</t>
         </is>
       </c>
       <c r="B237" t="inlineStr">
@@ -45995,7 +46964,7 @@
         </is>
       </c>
       <c r="C237" s="2" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>0</v>
       </c>
       <c r="D237" s="2" t="n">
         <v>1e-06</v>
@@ -46010,7 +46979,7 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>satelite_energia_preservado</t>
+          <t>satelite_agua_preservado</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
@@ -46019,7 +46988,7 @@
         </is>
       </c>
       <c r="C238" s="2" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="D238" s="2" t="n">
         <v>1e-06</v>
@@ -46034,7 +47003,7 @@
     <row r="239">
       <c r="A239" t="inlineStr">
         <is>
-          <t>niveis_residuo_nao_negativo</t>
+          <t>satelite_energia_preservado</t>
         </is>
       </c>
       <c r="B239" t="inlineStr">
@@ -46043,16 +47012,12 @@
         </is>
       </c>
       <c r="C239" s="2" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="D239" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E239" t="inlineStr">
-        <is>
-          <t>RS co2e (residuo): identificado 3862147.8290, resíduo 1975857.7254; RB co2e (residuo): identificado 34828615.1621, resíduo 49689733.8945</t>
-        </is>
-      </c>
+        <v>1e-06</v>
+      </c>
+      <c r="E239" t="inlineStr"/>
       <c r="F239" t="inlineStr">
         <is>
           <t>v04_rap_media</t>
@@ -46062,7 +47027,7 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>EOB_nao_negativo_subsetores</t>
+          <t>niveis_residuo_nao_negativo</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
@@ -46078,7 +47043,7 @@
       </c>
       <c r="E240" t="inlineStr">
         <is>
-          <t>todos ≥ 0</t>
+          <t>RS co2e (residuo): identificado 3862147.8290, resíduo 1975857.7254; RB co2e (residuo): identificado 34828615.1621, resíduo 49689733.8945</t>
         </is>
       </c>
       <c r="F240" t="inlineStr">
@@ -46090,7 +47055,7 @@
     <row r="241">
       <c r="A241" t="inlineStr">
         <is>
-          <t>subsetores_producao_zero_zerados</t>
+          <t>EOB_nao_negativo_subsetores</t>
         </is>
       </c>
       <c r="B241" t="inlineStr">
@@ -46099,14 +47064,14 @@
         </is>
       </c>
       <c r="C241" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D241" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E241" t="inlineStr">
         <is>
-          <t>3 subsetor(es) com produção zero: RS_S38_SOL, RS_S38_PET, RS_S38_NUC</t>
+          <t>todos ≥ 0</t>
         </is>
       </c>
       <c r="F241" t="inlineStr">
@@ -46118,7 +47083,7 @@
     <row r="242">
       <c r="A242" t="inlineStr">
         <is>
-          <t>L_nao_negativa</t>
+          <t>subsetores_producao_zero_zerados</t>
         </is>
       </c>
       <c r="B242" t="inlineStr">
@@ -46127,12 +47092,16 @@
         </is>
       </c>
       <c r="C242" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D242" s="2" t="n">
-        <v>-1e-10</v>
-      </c>
-      <c r="E242" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E242" t="inlineStr">
+        <is>
+          <t>3 subsetor(es) com produção zero: RS_S38_SOL, RS_S38_PET, RS_S38_NUC</t>
+        </is>
+      </c>
       <c r="F242" t="inlineStr">
         <is>
           <t>v04_rap_media</t>
@@ -46142,7 +47111,7 @@
     <row r="243">
       <c r="A243" t="inlineStr">
         <is>
-          <t>L_diagonal_maior_igual_1</t>
+          <t>L_nao_negativa</t>
         </is>
       </c>
       <c r="B243" t="inlineStr">
@@ -46151,10 +47120,10 @@
         </is>
       </c>
       <c r="C243" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D243" s="2" t="n">
-        <v>1</v>
+        <v>-1e-10</v>
       </c>
       <c r="E243" t="inlineStr"/>
       <c r="F243" t="inlineStr">
@@ -46166,7 +47135,7 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>A_soma_colunas_menor_1</t>
+          <t>L_diagonal_maior_igual_1</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
@@ -46175,16 +47144,12 @@
         </is>
       </c>
       <c r="C244" s="2" t="n">
-        <v>0.8542079132814551</v>
+        <v>1</v>
       </c>
       <c r="D244" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E244" t="inlineStr">
-        <is>
-          <t>Σ coeficientes técnicos de cada coluna (inclui latentes)</t>
-        </is>
-      </c>
+      <c r="E244" t="inlineStr"/>
       <c r="F244" t="inlineStr">
         <is>
           <t>v04_rap_media</t>
@@ -46194,7 +47159,7 @@
     <row r="245">
       <c r="A245" t="inlineStr">
         <is>
-          <t>RAS_convergencia</t>
+          <t>A_soma_colunas_menor_1</t>
         </is>
       </c>
       <c r="B245" t="inlineStr">
@@ -46203,14 +47168,14 @@
         </is>
       </c>
       <c r="C245" s="2" t="n">
-        <v>22</v>
+        <v>0.8542079132814551</v>
       </c>
       <c r="D245" s="2" t="n">
-        <v>20000</v>
+        <v>1</v>
       </c>
       <c r="E245" t="inlineStr">
         <is>
-          <t>linhas RS S38: necessário, convergiu em 22 iterações, erro 4.98e-09 (inicial 4.21e-01); linhas RB S38: necessário, convergiu em 21 iterações, erro 8.56e-09 (inicial 1.38e+00); reequilibrio_EOB RS (η = 0.1): necessário, convergiu em 7 iterações, erro 1.03e-09 (inicial 1.26e+02); reequilibrio_EOB RB (η = 0.1): necessário, convergiu em 8 iterações, erro 8.59e-10 (inicial 2.57e+03)</t>
+          <t>Σ coeficientes técnicos de cada coluna (inclui latentes)</t>
         </is>
       </c>
       <c r="F245" t="inlineStr">
@@ -46222,7 +47187,7 @@
     <row r="246">
       <c r="A246" t="inlineStr">
         <is>
-          <t>roteamento_vendas_geracao_igual_E</t>
+          <t>RAS_convergencia</t>
         </is>
       </c>
       <c r="B246" t="inlineStr">
@@ -46231,14 +47196,14 @@
         </is>
       </c>
       <c r="C246" s="2" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>22</v>
       </c>
       <c r="D246" s="2" t="n">
-        <v>1e-06</v>
+        <v>20000</v>
       </c>
       <c r="E246" t="inlineStr">
         <is>
-          <t>Σ vendas da geração de r dentro do bloco = E_r = F_r − T_r − G_r</t>
+          <t>linhas RS S38: necessário, convergiu em 22 iterações, erro 4.98e-09 (inicial 4.21e-01); linhas RB S38: necessário, convergiu em 21 iterações, erro 8.56e-09 (inicial 1.38e+00); reequilibrio_EOB RS (η = 0.1): necessário, convergiu em 7 iterações, erro 1.03e-09 (inicial 1.26e+02); reequilibrio_EOB RB (η = 0.1): necessário, convergiu em 8 iterações, erro 8.59e-10 (inicial 2.57e+03)</t>
         </is>
       </c>
       <c r="F246" t="inlineStr">
@@ -46250,7 +47215,7 @@
     <row r="247">
       <c r="A247" t="inlineStr">
         <is>
-          <t>roteamento_vendas_transmissao_igual_T</t>
+          <t>roteamento_vendas_geracao_igual_E</t>
         </is>
       </c>
       <c r="B247" t="inlineStr">
@@ -46259,14 +47224,14 @@
         </is>
       </c>
       <c r="C247" s="2" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="D247" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E247" t="inlineStr">
         <is>
-          <t>Σ vendas da transmissão de r dentro do bloco = T_r</t>
+          <t>Σ vendas da geração de r dentro do bloco = E_r = F_r − T_r − G_r</t>
         </is>
       </c>
       <c r="F247" t="inlineStr">
@@ -46278,7 +47243,7 @@
     <row r="248">
       <c r="A248" t="inlineStr">
         <is>
-          <t>roteamento_geracao_e_transmissao_nao_vendem_fora</t>
+          <t>roteamento_vendas_transmissao_igual_T</t>
         </is>
       </c>
       <c r="B248" t="inlineStr">
@@ -46294,7 +47259,7 @@
       </c>
       <c r="E248" t="inlineStr">
         <is>
-          <t>Σ |vendas| da geração e da transmissão fora do bloco e à demanda final (Seção 6.4)</t>
+          <t>Σ vendas da transmissão de r dentro do bloco = T_r</t>
         </is>
       </c>
       <c r="F248" t="inlineStr">
@@ -46306,7 +47271,7 @@
     <row r="249">
       <c r="A249" t="inlineStr">
         <is>
-          <t>roteamento_fracao_transmissao</t>
+          <t>roteamento_geracao_e_transmissao_nao_vendem_fora</t>
         </is>
       </c>
       <c r="B249" t="inlineStr">
@@ -46315,14 +47280,14 @@
         </is>
       </c>
       <c r="C249" s="2" t="n">
-        <v>7.781984822181929e-17</v>
+        <v>0</v>
       </c>
       <c r="D249" s="2" t="n">
-        <v>1e-09</v>
+        <v>1e-06</v>
       </c>
       <c r="E249" t="inlineStr">
         <is>
-          <t>fração da transmissão paga pela distribuição e pela geração das regiões desagregadas (o S38 agregado de região não desagregada recebe a sua parte inteira)</t>
+          <t>Σ |vendas| da geração e da transmissão fora do bloco e à demanda final (Seção 6.4)</t>
         </is>
       </c>
       <c r="F249" t="inlineStr">
@@ -46334,7 +47299,7 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>bloco_fluxos_regionais_preservados</t>
+          <t>roteamento_fracao_transmissao</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
@@ -46343,14 +47308,14 @@
         </is>
       </c>
       <c r="C250" s="2" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>7.781984822181929e-17</v>
       </c>
       <c r="D250" s="2" t="n">
-        <v>1e-06</v>
+        <v>1e-09</v>
       </c>
       <c r="E250" t="inlineStr">
         <is>
-          <t>os fluxos alvo→alvo entre as regiões (ex.: RS→RS, RS→RB, RB→RS, RB→RB) são os da original</t>
+          <t>fração da transmissão paga pela distribuição e pela geração das regiões desagregadas (o S38 agregado de região não desagregada recebe a sua parte inteira)</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -46362,7 +47327,7 @@
     <row r="251">
       <c r="A251" t="inlineStr">
         <is>
-          <t>subsetores_latentes</t>
+          <t>bloco_fluxos_regionais_preservados</t>
         </is>
       </c>
       <c r="B251" t="inlineStr">
@@ -46371,14 +47336,14 @@
         </is>
       </c>
       <c r="C251" s="2" t="n">
-        <v>2</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="D251" s="2" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="E251" t="inlineStr">
         <is>
-          <t>colunas de coeficientes guardadas à parte: RS_S38_SOL, RS_S38_PET</t>
+          <t>os fluxos alvo→alvo entre as regiões (ex.: RS→RS, RS→RB, RB→RS, RB→RB) são os da original</t>
         </is>
       </c>
       <c r="F251" t="inlineStr">
@@ -46390,7 +47355,7 @@
     <row r="252">
       <c r="A252" t="inlineStr">
         <is>
-          <t>piso_vbp_combustivel</t>
+          <t>subsetores_latentes</t>
         </is>
       </c>
       <c r="B252" t="inlineStr">
@@ -46399,14 +47364,14 @@
         </is>
       </c>
       <c r="C252" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D252" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E252" t="inlineStr">
         <is>
-          <t>VBP ≥ combustível ÷ κ (κ = 0.7); RS_S38_BIO: combustível/VBP = 0.0255; RS_S38_CAR: combustível/VBP = 0.0219; RS_S38_GN: combustível/VBP = 0.7000; RB_S38_BIO: combustível/VBP = 0.0204; RB_S38_CAR: combustível/VBP = 0.1077; RB_S38_GN: combustível/VBP = 0.7000; RB_S38_PET: combustível/VBP = 0.7000</t>
+          <t>colunas de coeficientes guardadas à parte: RS_S38_SOL, RS_S38_PET</t>
         </is>
       </c>
       <c r="F252" t="inlineStr">
@@ -46418,7 +47383,7 @@
     <row r="253">
       <c r="A253" t="inlineStr">
         <is>
-          <t>EOB_minimo_eta</t>
+          <t>piso_vbp_combustivel</t>
         </is>
       </c>
       <c r="B253" t="inlineStr">
@@ -46427,14 +47392,14 @@
         </is>
       </c>
       <c r="C253" s="2" t="n">
-        <v>0.09999999999999999</v>
+        <v>0</v>
       </c>
       <c r="D253" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E253" t="inlineStr">
         <is>
-          <t>EOB ≥ η × VBP (η = 0.1; tolerância absoluta 1e-06 R$ mi) em todo subsetor com produção</t>
+          <t>VBP ≥ combustível ÷ κ (κ = 0.7); RS_S38_BIO: combustível/VBP = 0.0255; RS_S38_CAR: combustível/VBP = 0.0219; RS_S38_GN: combustível/VBP = 0.7000; RB_S38_BIO: combustível/VBP = 0.0204; RB_S38_CAR: combustível/VBP = 0.1077; RB_S38_GN: combustível/VBP = 0.7000; RB_S38_PET: combustível/VBP = 0.7000</t>
         </is>
       </c>
       <c r="F253" t="inlineStr">
@@ -46446,7 +47411,7 @@
     <row r="254">
       <c r="A254" t="inlineStr">
         <is>
-          <t>reequilibrio_insumos_fixos</t>
+          <t>EOB_minimo_eta</t>
         </is>
       </c>
       <c r="B254" t="inlineStr">
@@ -46455,14 +47420,14 @@
         </is>
       </c>
       <c r="C254" s="2" t="n">
-        <v>0</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="D254" s="2" t="n">
-        <v>1e-06</v>
+        <v>0.1</v>
       </c>
       <c r="E254" t="inlineStr">
         <is>
-          <t>bloco, combustíveis, importações, remunerações e impostos sobre a produção iguais antes e depois do reequilíbrio</t>
+          <t>EOB ≥ η × VBP (η = 0.1; tolerância absoluta 1e-06 R$ mi) em todo subsetor com produção</t>
         </is>
       </c>
       <c r="F254" t="inlineStr">
@@ -46474,7 +47439,7 @@
     <row r="255">
       <c r="A255" t="inlineStr">
         <is>
-          <t>reequilibrio_soma_EOB_regiao</t>
+          <t>reequilibrio_insumos_fixos</t>
         </is>
       </c>
       <c r="B255" t="inlineStr">
@@ -46483,14 +47448,14 @@
         </is>
       </c>
       <c r="C255" s="2" t="n">
-        <v>4.365574568510056e-11</v>
+        <v>0</v>
       </c>
       <c r="D255" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E255" t="inlineStr">
         <is>
-          <t>Σ EOB dos subsetores de cada região = EOB original do setor-alvo; RB: Σ EOB = 103643.5529; RS: Σ EOB = 6737.4468</t>
+          <t>bloco, combustíveis, importações, remunerações e impostos sobre a produção iguais antes e depois do reequilíbrio</t>
         </is>
       </c>
       <c r="F255" t="inlineStr">
@@ -46502,23 +47467,23 @@
     <row r="256">
       <c r="A256" t="inlineStr">
         <is>
-          <t>insumos_nao_energeticos_minimo</t>
+          <t>reequilibrio_soma_EOB_regiao</t>
         </is>
       </c>
       <c r="B256" t="inlineStr">
         <is>
-          <t>ALERTA</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="C256" s="2" t="n">
-        <v>0.01995518999044971</v>
+        <v>4.365574568510056e-11</v>
       </c>
       <c r="D256" s="2" t="n">
-        <v>0.05</v>
+        <v>1e-06</v>
       </c>
       <c r="E256" t="inlineStr">
         <is>
-          <t>compras a setores fora do bloco, exceto combustíveis, ÷ VBP ≥ 0.05 em todo subsetor com produção: abaixo em RS_S38_GN (0.0200), RB_S38_GN (0.0265)</t>
+          <t>Σ EOB dos subsetores de cada região = EOB original do setor-alvo; RB: Σ EOB = 103643.5529; RS: Σ EOB = 6737.4468</t>
         </is>
       </c>
       <c r="F256" t="inlineStr">
@@ -46530,7 +47495,7 @@
     <row r="257">
       <c r="A257" t="inlineStr">
         <is>
-          <t>multiplicador_producao_subsetores</t>
+          <t>insumos_nao_energeticos_minimo</t>
         </is>
       </c>
       <c r="B257" t="inlineStr">
@@ -46539,14 +47504,14 @@
         </is>
       </c>
       <c r="C257" s="2" t="n">
-        <v>2.803945031536532</v>
+        <v>0.01995518999044971</v>
       </c>
       <c r="D257" s="2" t="n">
-        <v>2.2</v>
+        <v>0.05</v>
       </c>
       <c r="E257" t="inlineStr">
         <is>
-          <t>multiplicador de produção (Σ coluna de L, inclui latentes) ≤ 2.2: acima em RS_S38_GN (2.400), RS_S38_PET (2.804), RS_S38_GAS (2.344), RB_S38_PET (2.759)</t>
+          <t>compras a setores fora do bloco, exceto combustíveis, ÷ VBP ≥ 0.05 em todo subsetor com produção: abaixo em RS_S38_GN (0.0200), RB_S38_GN (0.0265)</t>
         </is>
       </c>
       <c r="F257" t="inlineStr">
@@ -46558,35 +47523,35 @@
     <row r="258">
       <c r="A258" t="inlineStr">
         <is>
-          <t>reagregacao_Z</t>
+          <t>multiplicador_producao_subsetores</t>
         </is>
       </c>
       <c r="B258" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>ALERTA</t>
         </is>
       </c>
       <c r="C258" s="2" t="n">
-        <v>2.120827957696747e-10</v>
+        <v>2.803945031536532</v>
       </c>
       <c r="D258" s="2" t="n">
-        <v>1e-06</v>
+        <v>2.2</v>
       </c>
       <c r="E258" t="inlineStr">
         <is>
-          <t>máx |Σ subsetores − original|</t>
+          <t>multiplicador de produção (Σ coluna de L, inclui latentes) ≤ 2.2: acima em RS_S38_GN (2.400), RS_S38_PET (2.804), RS_S38_GAS (2.344), RB_S38_PET (2.759)</t>
         </is>
       </c>
       <c r="F258" t="inlineStr">
         <is>
-          <t>v04_k060</t>
+          <t>v04_rap_media</t>
         </is>
       </c>
     </row>
     <row r="259">
       <c r="A259" t="inlineStr">
         <is>
-          <t>reagregacao_F</t>
+          <t>reagregacao_Z</t>
         </is>
       </c>
       <c r="B259" t="inlineStr">
@@ -46595,7 +47560,7 @@
         </is>
       </c>
       <c r="C259" s="2" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>2.120827957696747e-10</v>
       </c>
       <c r="D259" s="2" t="n">
         <v>1e-06</v>
@@ -46614,7 +47579,7 @@
     <row r="260">
       <c r="A260" t="inlineStr">
         <is>
-          <t>reagregacao_X</t>
+          <t>reagregacao_F</t>
         </is>
       </c>
       <c r="B260" t="inlineStr">
@@ -46623,7 +47588,7 @@
         </is>
       </c>
       <c r="C260" s="2" t="n">
-        <v>3.637978807091713e-12</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="D260" s="2" t="n">
         <v>1e-06</v>
@@ -46642,7 +47607,7 @@
     <row r="261">
       <c r="A261" t="inlineStr">
         <is>
-          <t>reagregacao_total_linha</t>
+          <t>reagregacao_X</t>
         </is>
       </c>
       <c r="B261" t="inlineStr">
@@ -46670,7 +47635,7 @@
     <row r="262">
       <c r="A262" t="inlineStr">
         <is>
-          <t>reagregacao_V</t>
+          <t>reagregacao_total_linha</t>
         </is>
       </c>
       <c r="B262" t="inlineStr">
@@ -46679,7 +47644,7 @@
         </is>
       </c>
       <c r="C262" s="2" t="n">
-        <v>1.332864485448226e-09</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="D262" s="2" t="n">
         <v>1e-06</v>
@@ -46698,7 +47663,7 @@
     <row r="263">
       <c r="A263" t="inlineStr">
         <is>
-          <t>reagregacao_S</t>
+          <t>reagregacao_V</t>
         </is>
       </c>
       <c r="B263" t="inlineStr">
@@ -46707,7 +47672,7 @@
         </is>
       </c>
       <c r="C263" s="2" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>1.332864485448226e-09</v>
       </c>
       <c r="D263" s="2" t="n">
         <v>1e-06</v>
@@ -46726,7 +47691,7 @@
     <row r="264">
       <c r="A264" t="inlineStr">
         <is>
-          <t>reagregacao_V_df</t>
+          <t>reagregacao_S</t>
         </is>
       </c>
       <c r="B264" t="inlineStr">
@@ -46735,7 +47700,7 @@
         </is>
       </c>
       <c r="C264" s="2" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="D264" s="2" t="n">
         <v>1e-06</v>
@@ -46754,7 +47719,7 @@
     <row r="265">
       <c r="A265" t="inlineStr">
         <is>
-          <t>reagregacao_X_df</t>
+          <t>reagregacao_V_df</t>
         </is>
       </c>
       <c r="B265" t="inlineStr">
@@ -46782,7 +47747,7 @@
     <row r="266">
       <c r="A266" t="inlineStr">
         <is>
-          <t>reagregacao_totais_EV</t>
+          <t>reagregacao_X_df</t>
         </is>
       </c>
       <c r="B266" t="inlineStr">
@@ -46796,7 +47761,11 @@
       <c r="D266" s="2" t="n">
         <v>1e-06</v>
       </c>
-      <c r="E266" t="inlineStr"/>
+      <c r="E266" t="inlineStr">
+        <is>
+          <t>máx |Σ subsetores − original|</t>
+        </is>
+      </c>
       <c r="F266" t="inlineStr">
         <is>
           <t>v04_k060</t>
@@ -46806,7 +47775,7 @@
     <row r="267">
       <c r="A267" t="inlineStr">
         <is>
-          <t>balanco_linha_subsetores</t>
+          <t>reagregacao_totais_EV</t>
         </is>
       </c>
       <c r="B267" t="inlineStr">
@@ -46815,16 +47784,12 @@
         </is>
       </c>
       <c r="C267" s="2" t="n">
-        <v>8.552888175472617e-09</v>
+        <v>0</v>
       </c>
       <c r="D267" s="2" t="n">
         <v>1e-06</v>
       </c>
-      <c r="E267" t="inlineStr">
-        <is>
-          <t>máx |Σ vendas − VBP| nos subsetores (tolerância + resíduo original × participação)</t>
-        </is>
-      </c>
+      <c r="E267" t="inlineStr"/>
       <c r="F267" t="inlineStr">
         <is>
           <t>v04_k060</t>
@@ -46834,7 +47799,7 @@
     <row r="268">
       <c r="A268" t="inlineStr">
         <is>
-          <t>balanco_coluna_subsetores</t>
+          <t>balanco_linha_subsetores</t>
         </is>
       </c>
       <c r="B268" t="inlineStr">
@@ -46843,14 +47808,14 @@
         </is>
       </c>
       <c r="C268" s="2" t="n">
-        <v>1.290034854113664e-11</v>
+        <v>8.552888175472617e-09</v>
       </c>
       <c r="D268" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E268" t="inlineStr">
         <is>
-          <t>máx |resíduo da coluna − participação × resíduo original| (o resíduo original é repartido pelo VBP)</t>
+          <t>máx |Σ vendas − VBP| nos subsetores (tolerância + resíduo original × participação)</t>
         </is>
       </c>
       <c r="F268" t="inlineStr">
@@ -46862,7 +47827,7 @@
     <row r="269">
       <c r="A269" t="inlineStr">
         <is>
-          <t>identidade_VA_subsetores</t>
+          <t>balanco_coluna_subsetores</t>
         </is>
       </c>
       <c r="B269" t="inlineStr">
@@ -46871,14 +47836,14 @@
         </is>
       </c>
       <c r="C269" s="2" t="n">
-        <v>2.091837814077735e-11</v>
+        <v>1.290034854113664e-11</v>
       </c>
       <c r="D269" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E269" t="inlineStr">
         <is>
-          <t>VA − (remunerações + EOB + impostos sobre a produção)</t>
+          <t>máx |resíduo da coluna − participação × resíduo original| (o resíduo original é repartido pelo VBP)</t>
         </is>
       </c>
       <c r="F269" t="inlineStr">
@@ -46890,7 +47855,7 @@
     <row r="270">
       <c r="A270" t="inlineStr">
         <is>
-          <t>nao_negatividade</t>
+          <t>identidade_VA_subsetores</t>
         </is>
       </c>
       <c r="B270" t="inlineStr">
@@ -46899,14 +47864,14 @@
         </is>
       </c>
       <c r="C270" s="2" t="n">
-        <v>0</v>
+        <v>2.091837814077735e-11</v>
       </c>
       <c r="D270" s="2" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="E270" t="inlineStr">
         <is>
-          <t>negativos só onde a original já tem (coluna de discrepância, EOB, impostos sobre a produção); nenhum negativo novo</t>
+          <t>VA − (remunerações + EOB + impostos sobre a produção)</t>
         </is>
       </c>
       <c r="F270" t="inlineStr">
@@ -46918,7 +47883,7 @@
     <row r="271">
       <c r="A271" t="inlineStr">
         <is>
-          <t>satelite_ocupacoes_preservado</t>
+          <t>nao_negatividade</t>
         </is>
       </c>
       <c r="B271" t="inlineStr">
@@ -46927,12 +47892,16 @@
         </is>
       </c>
       <c r="C271" s="2" t="n">
-        <v>2.91038304567337e-11</v>
+        <v>0</v>
       </c>
       <c r="D271" s="2" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="E271" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E271" t="inlineStr">
+        <is>
+          <t>negativos só onde a original já tem (coluna de discrepância, EOB, impostos sobre a produção); nenhum negativo novo</t>
+        </is>
+      </c>
       <c r="F271" t="inlineStr">
         <is>
           <t>v04_k060</t>
@@ -46942,7 +47911,7 @@
     <row r="272">
       <c r="A272" t="inlineStr">
         <is>
-          <t>satelite_co2e_preservado</t>
+          <t>satelite_ocupacoes_preservado</t>
         </is>
       </c>
       <c r="B272" t="inlineStr">
@@ -46951,7 +47920,7 @@
         </is>
       </c>
       <c r="C272" s="2" t="n">
-        <v>0</v>
+        <v>2.91038304567337e-11</v>
       </c>
       <c r="D272" s="2" t="n">
         <v>1e-06</v>
@@ -46966,7 +47935,7 @@
     <row r="273">
       <c r="A273" t="inlineStr">
         <is>
-          <t>satelite_agua_preservado</t>
+          <t>satelite_co2e_preservado</t>
         </is>
       </c>
       <c r="B273" t="inlineStr">
@@ -46975,7 +47944,7 @@
         </is>
       </c>
       <c r="C273" s="2" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>0</v>
       </c>
       <c r="D273" s="2" t="n">
         <v>1e-06</v>
@@ -46990,7 +47959,7 @@
     <row r="274">
       <c r="A274" t="inlineStr">
         <is>
-          <t>satelite_energia_preservado</t>
+          <t>satelite_agua_preservado</t>
         </is>
       </c>
       <c r="B274" t="inlineStr">
@@ -46999,7 +47968,7 @@
         </is>
       </c>
       <c r="C274" s="2" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="D274" s="2" t="n">
         <v>1e-06</v>
@@ -47014,7 +47983,7 @@
     <row r="275">
       <c r="A275" t="inlineStr">
         <is>
-          <t>niveis_residuo_nao_negativo</t>
+          <t>satelite_energia_preservado</t>
         </is>
       </c>
       <c r="B275" t="inlineStr">
@@ -47023,16 +47992,12 @@
         </is>
       </c>
       <c r="C275" s="2" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="D275" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E275" t="inlineStr">
-        <is>
-          <t>RS co2e (residuo): identificado 3862147.8290, resíduo 1975857.7254; RB co2e (residuo): identificado 34828615.1621, resíduo 49689733.8945</t>
-        </is>
-      </c>
+        <v>1e-06</v>
+      </c>
+      <c r="E275" t="inlineStr"/>
       <c r="F275" t="inlineStr">
         <is>
           <t>v04_k060</t>
@@ -47042,7 +48007,7 @@
     <row r="276">
       <c r="A276" t="inlineStr">
         <is>
-          <t>EOB_nao_negativo_subsetores</t>
+          <t>niveis_residuo_nao_negativo</t>
         </is>
       </c>
       <c r="B276" t="inlineStr">
@@ -47058,7 +48023,7 @@
       </c>
       <c r="E276" t="inlineStr">
         <is>
-          <t>todos ≥ 0</t>
+          <t>RS co2e (residuo): identificado 3862147.8290, resíduo 1975857.7254; RB co2e (residuo): identificado 34828615.1621, resíduo 49689733.8945</t>
         </is>
       </c>
       <c r="F276" t="inlineStr">
@@ -47070,7 +48035,7 @@
     <row r="277">
       <c r="A277" t="inlineStr">
         <is>
-          <t>subsetores_producao_zero_zerados</t>
+          <t>EOB_nao_negativo_subsetores</t>
         </is>
       </c>
       <c r="B277" t="inlineStr">
@@ -47079,14 +48044,14 @@
         </is>
       </c>
       <c r="C277" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D277" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E277" t="inlineStr">
         <is>
-          <t>3 subsetor(es) com produção zero: RS_S38_SOL, RS_S38_PET, RS_S38_NUC</t>
+          <t>todos ≥ 0</t>
         </is>
       </c>
       <c r="F277" t="inlineStr">
@@ -47098,7 +48063,7 @@
     <row r="278">
       <c r="A278" t="inlineStr">
         <is>
-          <t>L_nao_negativa</t>
+          <t>subsetores_producao_zero_zerados</t>
         </is>
       </c>
       <c r="B278" t="inlineStr">
@@ -47107,12 +48072,16 @@
         </is>
       </c>
       <c r="C278" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D278" s="2" t="n">
-        <v>-1e-10</v>
-      </c>
-      <c r="E278" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E278" t="inlineStr">
+        <is>
+          <t>3 subsetor(es) com produção zero: RS_S38_SOL, RS_S38_PET, RS_S38_NUC</t>
+        </is>
+      </c>
       <c r="F278" t="inlineStr">
         <is>
           <t>v04_k060</t>
@@ -47122,7 +48091,7 @@
     <row r="279">
       <c r="A279" t="inlineStr">
         <is>
-          <t>L_diagonal_maior_igual_1</t>
+          <t>L_nao_negativa</t>
         </is>
       </c>
       <c r="B279" t="inlineStr">
@@ -47131,10 +48100,10 @@
         </is>
       </c>
       <c r="C279" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D279" s="2" t="n">
-        <v>1</v>
+        <v>-1e-10</v>
       </c>
       <c r="E279" t="inlineStr"/>
       <c r="F279" t="inlineStr">
@@ -47146,7 +48115,7 @@
     <row r="280">
       <c r="A280" t="inlineStr">
         <is>
-          <t>A_soma_colunas_menor_1</t>
+          <t>L_diagonal_maior_igual_1</t>
         </is>
       </c>
       <c r="B280" t="inlineStr">
@@ -47155,16 +48124,12 @@
         </is>
       </c>
       <c r="C280" s="2" t="n">
-        <v>0.8333826740734934</v>
+        <v>1</v>
       </c>
       <c r="D280" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E280" t="inlineStr">
-        <is>
-          <t>Σ coeficientes técnicos de cada coluna (inclui latentes)</t>
-        </is>
-      </c>
+      <c r="E280" t="inlineStr"/>
       <c r="F280" t="inlineStr">
         <is>
           <t>v04_k060</t>
@@ -47174,7 +48139,7 @@
     <row r="281">
       <c r="A281" t="inlineStr">
         <is>
-          <t>RAS_convergencia</t>
+          <t>A_soma_colunas_menor_1</t>
         </is>
       </c>
       <c r="B281" t="inlineStr">
@@ -47183,14 +48148,14 @@
         </is>
       </c>
       <c r="C281" s="2" t="n">
-        <v>22</v>
+        <v>0.8333826740734934</v>
       </c>
       <c r="D281" s="2" t="n">
-        <v>20000</v>
+        <v>1</v>
       </c>
       <c r="E281" t="inlineStr">
         <is>
-          <t>linhas RS S38: necessário, convergiu em 22 iterações, erro 4.98e-09 (inicial 4.21e-01); linhas RB S38: necessário, convergiu em 21 iterações, erro 8.56e-09 (inicial 1.38e+00); reequilibrio_EOB RS (η = 0.1): necessário, convergiu em 7 iterações, erro 1.33e-09 (inicial 1.26e+02); reequilibrio_EOB RB (η = 0.1): necessário, convergiu em 8 iterações, erro 3.24e-10 (inicial 1.40e+03)</t>
+          <t>Σ coeficientes técnicos de cada coluna (inclui latentes)</t>
         </is>
       </c>
       <c r="F281" t="inlineStr">
@@ -47202,7 +48167,7 @@
     <row r="282">
       <c r="A282" t="inlineStr">
         <is>
-          <t>roteamento_vendas_geracao_igual_E</t>
+          <t>RAS_convergencia</t>
         </is>
       </c>
       <c r="B282" t="inlineStr">
@@ -47211,14 +48176,14 @@
         </is>
       </c>
       <c r="C282" s="2" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>22</v>
       </c>
       <c r="D282" s="2" t="n">
-        <v>1e-06</v>
+        <v>20000</v>
       </c>
       <c r="E282" t="inlineStr">
         <is>
-          <t>Σ vendas da geração de r dentro do bloco = E_r = F_r − T_r − G_r</t>
+          <t>linhas RS S38: necessário, convergiu em 22 iterações, erro 4.98e-09 (inicial 4.21e-01); linhas RB S38: necessário, convergiu em 21 iterações, erro 8.56e-09 (inicial 1.38e+00); reequilibrio_EOB RS (η = 0.1): necessário, convergiu em 7 iterações, erro 1.33e-09 (inicial 1.26e+02); reequilibrio_EOB RB (η = 0.1): necessário, convergiu em 8 iterações, erro 3.24e-10 (inicial 1.40e+03)</t>
         </is>
       </c>
       <c r="F282" t="inlineStr">
@@ -47230,7 +48195,7 @@
     <row r="283">
       <c r="A283" t="inlineStr">
         <is>
-          <t>roteamento_vendas_transmissao_igual_T</t>
+          <t>roteamento_vendas_geracao_igual_E</t>
         </is>
       </c>
       <c r="B283" t="inlineStr">
@@ -47239,14 +48204,14 @@
         </is>
       </c>
       <c r="C283" s="2" t="n">
-        <v>0</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="D283" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E283" t="inlineStr">
         <is>
-          <t>Σ vendas da transmissão de r dentro do bloco = T_r</t>
+          <t>Σ vendas da geração de r dentro do bloco = E_r = F_r − T_r − G_r</t>
         </is>
       </c>
       <c r="F283" t="inlineStr">
@@ -47258,7 +48223,7 @@
     <row r="284">
       <c r="A284" t="inlineStr">
         <is>
-          <t>roteamento_geracao_e_transmissao_nao_vendem_fora</t>
+          <t>roteamento_vendas_transmissao_igual_T</t>
         </is>
       </c>
       <c r="B284" t="inlineStr">
@@ -47274,7 +48239,7 @@
       </c>
       <c r="E284" t="inlineStr">
         <is>
-          <t>Σ |vendas| da geração e da transmissão fora do bloco e à demanda final (Seção 6.4)</t>
+          <t>Σ vendas da transmissão de r dentro do bloco = T_r</t>
         </is>
       </c>
       <c r="F284" t="inlineStr">
@@ -47286,7 +48251,7 @@
     <row r="285">
       <c r="A285" t="inlineStr">
         <is>
-          <t>roteamento_fracao_transmissao</t>
+          <t>roteamento_geracao_e_transmissao_nao_vendem_fora</t>
         </is>
       </c>
       <c r="B285" t="inlineStr">
@@ -47295,14 +48260,14 @@
         </is>
       </c>
       <c r="C285" s="2" t="n">
-        <v>8.173395242890144e-17</v>
+        <v>0</v>
       </c>
       <c r="D285" s="2" t="n">
-        <v>1e-09</v>
+        <v>1e-06</v>
       </c>
       <c r="E285" t="inlineStr">
         <is>
-          <t>fração da transmissão paga pela distribuição e pela geração das regiões desagregadas (o S38 agregado de região não desagregada recebe a sua parte inteira)</t>
+          <t>Σ |vendas| da geração e da transmissão fora do bloco e à demanda final (Seção 6.4)</t>
         </is>
       </c>
       <c r="F285" t="inlineStr">
@@ -47314,7 +48279,7 @@
     <row r="286">
       <c r="A286" t="inlineStr">
         <is>
-          <t>bloco_fluxos_regionais_preservados</t>
+          <t>roteamento_fracao_transmissao</t>
         </is>
       </c>
       <c r="B286" t="inlineStr">
@@ -47323,14 +48288,14 @@
         </is>
       </c>
       <c r="C286" s="2" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>8.173395242890144e-17</v>
       </c>
       <c r="D286" s="2" t="n">
-        <v>1e-06</v>
+        <v>1e-09</v>
       </c>
       <c r="E286" t="inlineStr">
         <is>
-          <t>os fluxos alvo→alvo entre as regiões (ex.: RS→RS, RS→RB, RB→RS, RB→RB) são os da original</t>
+          <t>fração da transmissão paga pela distribuição e pela geração das regiões desagregadas (o S38 agregado de região não desagregada recebe a sua parte inteira)</t>
         </is>
       </c>
       <c r="F286" t="inlineStr">
@@ -47342,7 +48307,7 @@
     <row r="287">
       <c r="A287" t="inlineStr">
         <is>
-          <t>subsetores_latentes</t>
+          <t>bloco_fluxos_regionais_preservados</t>
         </is>
       </c>
       <c r="B287" t="inlineStr">
@@ -47351,14 +48316,14 @@
         </is>
       </c>
       <c r="C287" s="2" t="n">
-        <v>2</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="D287" s="2" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="E287" t="inlineStr">
         <is>
-          <t>colunas de coeficientes guardadas à parte: RS_S38_SOL, RS_S38_PET</t>
+          <t>os fluxos alvo→alvo entre as regiões (ex.: RS→RS, RS→RB, RB→RS, RB→RB) são os da original</t>
         </is>
       </c>
       <c r="F287" t="inlineStr">
@@ -47370,7 +48335,7 @@
     <row r="288">
       <c r="A288" t="inlineStr">
         <is>
-          <t>piso_vbp_combustivel</t>
+          <t>subsetores_latentes</t>
         </is>
       </c>
       <c r="B288" t="inlineStr">
@@ -47379,14 +48344,14 @@
         </is>
       </c>
       <c r="C288" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D288" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E288" t="inlineStr">
         <is>
-          <t>VBP ≥ combustível ÷ κ (κ = 0.6); RS_S38_BIO: combustível/VBP = 0.0248; RS_S38_CAR: combustível/VBP = 0.0213; RS_S38_GN: combustível/VBP = 0.6000; RB_S38_BIO: combustível/VBP = 0.0206; RB_S38_CAR: combustível/VBP = 0.1090; RB_S38_GN: combustível/VBP = 0.6000; RB_S38_PET: combustível/VBP = 0.6000</t>
+          <t>colunas de coeficientes guardadas à parte: RS_S38_SOL, RS_S38_PET</t>
         </is>
       </c>
       <c r="F288" t="inlineStr">
@@ -47398,7 +48363,7 @@
     <row r="289">
       <c r="A289" t="inlineStr">
         <is>
-          <t>EOB_minimo_eta</t>
+          <t>piso_vbp_combustivel</t>
         </is>
       </c>
       <c r="B289" t="inlineStr">
@@ -47407,14 +48372,14 @@
         </is>
       </c>
       <c r="C289" s="2" t="n">
-        <v>0.09999999999999998</v>
+        <v>0</v>
       </c>
       <c r="D289" s="2" t="n">
-        <v>0.1</v>
+        <v>0</v>
       </c>
       <c r="E289" t="inlineStr">
         <is>
-          <t>EOB ≥ η × VBP (η = 0.1; tolerância absoluta 1e-06 R$ mi) em todo subsetor com produção</t>
+          <t>VBP ≥ combustível ÷ κ (κ = 0.6); RS_S38_BIO: combustível/VBP = 0.0248; RS_S38_CAR: combustível/VBP = 0.0213; RS_S38_GN: combustível/VBP = 0.6000; RB_S38_BIO: combustível/VBP = 0.0206; RB_S38_CAR: combustível/VBP = 0.1090; RB_S38_GN: combustível/VBP = 0.6000; RB_S38_PET: combustível/VBP = 0.6000</t>
         </is>
       </c>
       <c r="F289" t="inlineStr">
@@ -47426,7 +48391,7 @@
     <row r="290">
       <c r="A290" t="inlineStr">
         <is>
-          <t>reequilibrio_insumos_fixos</t>
+          <t>EOB_minimo_eta</t>
         </is>
       </c>
       <c r="B290" t="inlineStr">
@@ -47435,14 +48400,14 @@
         </is>
       </c>
       <c r="C290" s="2" t="n">
-        <v>0</v>
+        <v>0.09999999999999998</v>
       </c>
       <c r="D290" s="2" t="n">
-        <v>1e-06</v>
+        <v>0.1</v>
       </c>
       <c r="E290" t="inlineStr">
         <is>
-          <t>bloco, combustíveis, importações, remunerações e impostos sobre a produção iguais antes e depois do reequilíbrio</t>
+          <t>EOB ≥ η × VBP (η = 0.1; tolerância absoluta 1e-06 R$ mi) em todo subsetor com produção</t>
         </is>
       </c>
       <c r="F290" t="inlineStr">
@@ -47454,7 +48419,7 @@
     <row r="291">
       <c r="A291" t="inlineStr">
         <is>
-          <t>reequilibrio_soma_EOB_regiao</t>
+          <t>reequilibrio_insumos_fixos</t>
         </is>
       </c>
       <c r="B291" t="inlineStr">
@@ -47463,14 +48428,14 @@
         </is>
       </c>
       <c r="C291" s="2" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>0</v>
       </c>
       <c r="D291" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E291" t="inlineStr">
         <is>
-          <t>Σ EOB dos subsetores de cada região = EOB original do setor-alvo; RB: Σ EOB = 103643.5529; RS: Σ EOB = 6737.4468</t>
+          <t>bloco, combustíveis, importações, remunerações e impostos sobre a produção iguais antes e depois do reequilíbrio</t>
         </is>
       </c>
       <c r="F291" t="inlineStr">
@@ -47482,7 +48447,7 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>insumos_nao_energeticos_minimo</t>
+          <t>reequilibrio_soma_EOB_regiao</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
@@ -47491,14 +48456,14 @@
         </is>
       </c>
       <c r="C292" s="2" t="n">
-        <v>0.07680941610745359</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="D292" s="2" t="n">
-        <v>0.05</v>
+        <v>1e-06</v>
       </c>
       <c r="E292" t="inlineStr">
         <is>
-          <t>compras a setores fora do bloco, exceto combustíveis, ÷ VBP ≥ 0.05 em todo subsetor com produção</t>
+          <t>Σ EOB dos subsetores de cada região = EOB original do setor-alvo; RB: Σ EOB = 103643.5529; RS: Σ EOB = 6737.4468</t>
         </is>
       </c>
       <c r="F292" t="inlineStr">
@@ -47510,23 +48475,23 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>multiplicador_producao_subsetores</t>
+          <t>insumos_nao_energeticos_minimo</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>ALERTA</t>
+          <t>OK</t>
         </is>
       </c>
       <c r="C293" s="2" t="n">
-        <v>2.664034321340072</v>
+        <v>0.07680941610745359</v>
       </c>
       <c r="D293" s="2" t="n">
-        <v>2.2</v>
+        <v>0.05</v>
       </c>
       <c r="E293" t="inlineStr">
         <is>
-          <t>multiplicador de produção (Σ coluna de L, inclui latentes) ≤ 2.2: acima em RS_S38_GN (2.318), RS_S38_PET (2.664), RS_S38_GAS (2.344), RB_S38_PET (2.628)</t>
+          <t>compras a setores fora do bloco, exceto combustíveis, ÷ VBP ≥ 0.05 em todo subsetor com produção</t>
         </is>
       </c>
       <c r="F293" t="inlineStr">
@@ -47538,35 +48503,35 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>reagregacao_Z</t>
+          <t>multiplicador_producao_subsetores</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>OK</t>
+          <t>ALERTA</t>
         </is>
       </c>
       <c r="C294" s="2" t="n">
-        <v>1.882654032669961e-10</v>
+        <v>2.664034321340072</v>
       </c>
       <c r="D294" s="2" t="n">
-        <v>1e-06</v>
+        <v>2.2</v>
       </c>
       <c r="E294" t="inlineStr">
         <is>
-          <t>máx |Σ subsetores − original|</t>
+          <t>multiplicador de produção (Σ coluna de L, inclui latentes) ≤ 2.2: acima em RS_S38_GN (2.318), RS_S38_PET (2.664), RS_S38_GAS (2.344), RB_S38_PET (2.628)</t>
         </is>
       </c>
       <c r="F294" t="inlineStr">
         <is>
-          <t>v04_eta005</t>
+          <t>v04_k060</t>
         </is>
       </c>
     </row>
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>reagregacao_F</t>
+          <t>reagregacao_Z</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
@@ -47575,7 +48540,7 @@
         </is>
       </c>
       <c r="C295" s="2" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>1.882654032669961e-10</v>
       </c>
       <c r="D295" s="2" t="n">
         <v>1e-06</v>
@@ -47594,7 +48559,7 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>reagregacao_X</t>
+          <t>reagregacao_F</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
@@ -47603,7 +48568,7 @@
         </is>
       </c>
       <c r="C296" s="2" t="n">
-        <v>3.637978807091713e-12</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="D296" s="2" t="n">
         <v>1e-06</v>
@@ -47622,7 +48587,7 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>reagregacao_total_linha</t>
+          <t>reagregacao_X</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
@@ -47650,7 +48615,7 @@
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>reagregacao_V</t>
+          <t>reagregacao_total_linha</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
@@ -47659,7 +48624,7 @@
         </is>
       </c>
       <c r="C298" s="2" t="n">
-        <v>8.803908713161945e-10</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="D298" s="2" t="n">
         <v>1e-06</v>
@@ -47678,7 +48643,7 @@
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>reagregacao_S</t>
+          <t>reagregacao_V</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
@@ -47687,7 +48652,7 @@
         </is>
       </c>
       <c r="C299" s="2" t="n">
-        <v>1.818989403545856e-12</v>
+        <v>8.803908713161945e-10</v>
       </c>
       <c r="D299" s="2" t="n">
         <v>1e-06</v>
@@ -47706,7 +48671,7 @@
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>reagregacao_V_df</t>
+          <t>reagregacao_S</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
@@ -47715,7 +48680,7 @@
         </is>
       </c>
       <c r="C300" s="2" t="n">
-        <v>0</v>
+        <v>1.818989403545856e-12</v>
       </c>
       <c r="D300" s="2" t="n">
         <v>1e-06</v>
@@ -47734,7 +48699,7 @@
     <row r="301">
       <c r="A301" t="inlineStr">
         <is>
-          <t>reagregacao_X_df</t>
+          <t>reagregacao_V_df</t>
         </is>
       </c>
       <c r="B301" t="inlineStr">
@@ -47762,7 +48727,7 @@
     <row r="302">
       <c r="A302" t="inlineStr">
         <is>
-          <t>reagregacao_totais_EV</t>
+          <t>reagregacao_X_df</t>
         </is>
       </c>
       <c r="B302" t="inlineStr">
@@ -47776,7 +48741,11 @@
       <c r="D302" s="2" t="n">
         <v>1e-06</v>
       </c>
-      <c r="E302" t="inlineStr"/>
+      <c r="E302" t="inlineStr">
+        <is>
+          <t>máx |Σ subsetores − original|</t>
+        </is>
+      </c>
       <c r="F302" t="inlineStr">
         <is>
           <t>v04_eta005</t>
@@ -47786,7 +48755,7 @@
     <row r="303">
       <c r="A303" t="inlineStr">
         <is>
-          <t>balanco_linha_subsetores</t>
+          <t>reagregacao_totais_EV</t>
         </is>
       </c>
       <c r="B303" t="inlineStr">
@@ -47795,16 +48764,12 @@
         </is>
       </c>
       <c r="C303" s="2" t="n">
-        <v>8.552888175472617e-09</v>
+        <v>0</v>
       </c>
       <c r="D303" s="2" t="n">
         <v>1e-06</v>
       </c>
-      <c r="E303" t="inlineStr">
-        <is>
-          <t>máx |Σ vendas − VBP| nos subsetores (tolerância + resíduo original × participação)</t>
-        </is>
-      </c>
+      <c r="E303" t="inlineStr"/>
       <c r="F303" t="inlineStr">
         <is>
           <t>v04_eta005</t>
@@ -47814,7 +48779,7 @@
     <row r="304">
       <c r="A304" t="inlineStr">
         <is>
-          <t>balanco_coluna_subsetores</t>
+          <t>balanco_linha_subsetores</t>
         </is>
       </c>
       <c r="B304" t="inlineStr">
@@ -47823,14 +48788,14 @@
         </is>
       </c>
       <c r="C304" s="2" t="n">
-        <v>1.290034854113664e-11</v>
+        <v>8.552888175472617e-09</v>
       </c>
       <c r="D304" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E304" t="inlineStr">
         <is>
-          <t>máx |resíduo da coluna − participação × resíduo original| (o resíduo original é repartido pelo VBP)</t>
+          <t>máx |Σ vendas − VBP| nos subsetores (tolerância + resíduo original × participação)</t>
         </is>
       </c>
       <c r="F304" t="inlineStr">
@@ -47842,7 +48807,7 @@
     <row r="305">
       <c r="A305" t="inlineStr">
         <is>
-          <t>identidade_VA_subsetores</t>
+          <t>balanco_coluna_subsetores</t>
         </is>
       </c>
       <c r="B305" t="inlineStr">
@@ -47851,14 +48816,14 @@
         </is>
       </c>
       <c r="C305" s="2" t="n">
-        <v>2.091837814077735e-11</v>
+        <v>1.290034854113664e-11</v>
       </c>
       <c r="D305" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E305" t="inlineStr">
         <is>
-          <t>VA − (remunerações + EOB + impostos sobre a produção)</t>
+          <t>máx |resíduo da coluna − participação × resíduo original| (o resíduo original é repartido pelo VBP)</t>
         </is>
       </c>
       <c r="F305" t="inlineStr">
@@ -47870,7 +48835,7 @@
     <row r="306">
       <c r="A306" t="inlineStr">
         <is>
-          <t>nao_negatividade</t>
+          <t>identidade_VA_subsetores</t>
         </is>
       </c>
       <c r="B306" t="inlineStr">
@@ -47879,14 +48844,14 @@
         </is>
       </c>
       <c r="C306" s="2" t="n">
-        <v>0</v>
+        <v>2.091837814077735e-11</v>
       </c>
       <c r="D306" s="2" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="E306" t="inlineStr">
         <is>
-          <t>negativos só onde a original já tem (coluna de discrepância, EOB, impostos sobre a produção); nenhum negativo novo</t>
+          <t>VA − (remunerações + EOB + impostos sobre a produção)</t>
         </is>
       </c>
       <c r="F306" t="inlineStr">
@@ -47898,7 +48863,7 @@
     <row r="307">
       <c r="A307" t="inlineStr">
         <is>
-          <t>satelite_ocupacoes_preservado</t>
+          <t>nao_negatividade</t>
         </is>
       </c>
       <c r="B307" t="inlineStr">
@@ -47907,12 +48872,16 @@
         </is>
       </c>
       <c r="C307" s="2" t="n">
-        <v>3.637978807091713e-12</v>
+        <v>0</v>
       </c>
       <c r="D307" s="2" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="E307" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E307" t="inlineStr">
+        <is>
+          <t>negativos só onde a original já tem (coluna de discrepância, EOB, impostos sobre a produção); nenhum negativo novo</t>
+        </is>
+      </c>
       <c r="F307" t="inlineStr">
         <is>
           <t>v04_eta005</t>
@@ -47922,7 +48891,7 @@
     <row r="308">
       <c r="A308" t="inlineStr">
         <is>
-          <t>satelite_co2e_preservado</t>
+          <t>satelite_ocupacoes_preservado</t>
         </is>
       </c>
       <c r="B308" t="inlineStr">
@@ -47931,7 +48900,7 @@
         </is>
       </c>
       <c r="C308" s="2" t="n">
-        <v>0</v>
+        <v>3.637978807091713e-12</v>
       </c>
       <c r="D308" s="2" t="n">
         <v>1e-06</v>
@@ -47946,7 +48915,7 @@
     <row r="309">
       <c r="A309" t="inlineStr">
         <is>
-          <t>satelite_agua_preservado</t>
+          <t>satelite_co2e_preservado</t>
         </is>
       </c>
       <c r="B309" t="inlineStr">
@@ -47955,7 +48924,7 @@
         </is>
       </c>
       <c r="C309" s="2" t="n">
-        <v>1.77635683940025e-15</v>
+        <v>0</v>
       </c>
       <c r="D309" s="2" t="n">
         <v>1e-06</v>
@@ -47970,7 +48939,7 @@
     <row r="310">
       <c r="A310" t="inlineStr">
         <is>
-          <t>satelite_energia_preservado</t>
+          <t>satelite_agua_preservado</t>
         </is>
       </c>
       <c r="B310" t="inlineStr">
@@ -47979,7 +48948,7 @@
         </is>
       </c>
       <c r="C310" s="2" t="n">
-        <v>9.094947017729282e-13</v>
+        <v>1.77635683940025e-15</v>
       </c>
       <c r="D310" s="2" t="n">
         <v>1e-06</v>
@@ -47994,7 +48963,7 @@
     <row r="311">
       <c r="A311" t="inlineStr">
         <is>
-          <t>niveis_residuo_nao_negativo</t>
+          <t>satelite_energia_preservado</t>
         </is>
       </c>
       <c r="B311" t="inlineStr">
@@ -48003,16 +48972,12 @@
         </is>
       </c>
       <c r="C311" s="2" t="n">
-        <v>0</v>
+        <v>9.094947017729282e-13</v>
       </c>
       <c r="D311" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E311" t="inlineStr">
-        <is>
-          <t>RS co2e (residuo): identificado 3862147.8290, resíduo 1975857.7254; RB co2e (residuo): identificado 34828615.1621, resíduo 49689733.8945</t>
-        </is>
-      </c>
+        <v>1e-06</v>
+      </c>
+      <c r="E311" t="inlineStr"/>
       <c r="F311" t="inlineStr">
         <is>
           <t>v04_eta005</t>
@@ -48022,7 +48987,7 @@
     <row r="312">
       <c r="A312" t="inlineStr">
         <is>
-          <t>EOB_nao_negativo_subsetores</t>
+          <t>niveis_residuo_nao_negativo</t>
         </is>
       </c>
       <c r="B312" t="inlineStr">
@@ -48038,7 +49003,7 @@
       </c>
       <c r="E312" t="inlineStr">
         <is>
-          <t>todos ≥ 0</t>
+          <t>RS co2e (residuo): identificado 3862147.8290, resíduo 1975857.7254; RB co2e (residuo): identificado 34828615.1621, resíduo 49689733.8945</t>
         </is>
       </c>
       <c r="F312" t="inlineStr">
@@ -48050,7 +49015,7 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>subsetores_producao_zero_zerados</t>
+          <t>EOB_nao_negativo_subsetores</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
@@ -48059,14 +49024,14 @@
         </is>
       </c>
       <c r="C313" s="2" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="D313" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E313" t="inlineStr">
         <is>
-          <t>3 subsetor(es) com produção zero: RS_S38_SOL, RS_S38_PET, RS_S38_NUC</t>
+          <t>todos ≥ 0</t>
         </is>
       </c>
       <c r="F313" t="inlineStr">
@@ -48078,7 +49043,7 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>L_nao_negativa</t>
+          <t>subsetores_producao_zero_zerados</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
@@ -48087,12 +49052,16 @@
         </is>
       </c>
       <c r="C314" s="2" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="D314" s="2" t="n">
-        <v>-1e-10</v>
-      </c>
-      <c r="E314" t="inlineStr"/>
+        <v>0</v>
+      </c>
+      <c r="E314" t="inlineStr">
+        <is>
+          <t>3 subsetor(es) com produção zero: RS_S38_SOL, RS_S38_PET, RS_S38_NUC</t>
+        </is>
+      </c>
       <c r="F314" t="inlineStr">
         <is>
           <t>v04_eta005</t>
@@ -48102,7 +49071,7 @@
     <row r="315">
       <c r="A315" t="inlineStr">
         <is>
-          <t>L_diagonal_maior_igual_1</t>
+          <t>L_nao_negativa</t>
         </is>
       </c>
       <c r="B315" t="inlineStr">
@@ -48111,10 +49080,10 @@
         </is>
       </c>
       <c r="C315" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D315" s="2" t="n">
-        <v>1</v>
+        <v>-1e-10</v>
       </c>
       <c r="E315" t="inlineStr"/>
       <c r="F315" t="inlineStr">
@@ -48126,7 +49095,7 @@
     <row r="316">
       <c r="A316" t="inlineStr">
         <is>
-          <t>A_soma_colunas_menor_1</t>
+          <t>L_diagonal_maior_igual_1</t>
         </is>
       </c>
       <c r="B316" t="inlineStr">
@@ -48135,16 +49104,12 @@
         </is>
       </c>
       <c r="C316" s="2" t="n">
-        <v>0.8774713754987734</v>
+        <v>1</v>
       </c>
       <c r="D316" s="2" t="n">
         <v>1</v>
       </c>
-      <c r="E316" t="inlineStr">
-        <is>
-          <t>Σ coeficientes técnicos de cada coluna (inclui latentes)</t>
-        </is>
-      </c>
+      <c r="E316" t="inlineStr"/>
       <c r="F316" t="inlineStr">
         <is>
           <t>v04_eta005</t>
@@ -48154,7 +49119,7 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>RAS_convergencia</t>
+          <t>A_soma_colunas_menor_1</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
@@ -48163,14 +49128,14 @@
         </is>
       </c>
       <c r="C317" s="2" t="n">
-        <v>22</v>
+        <v>0.8774713754987734</v>
       </c>
       <c r="D317" s="2" t="n">
-        <v>20000</v>
+        <v>1</v>
       </c>
       <c r="E317" t="inlineStr">
         <is>
-          <t>linhas RS S38: necessário, convergiu em 22 iterações, erro 4.98e-09 (inicial 4.21e-01); linhas RB S38: necessário, convergiu em 21 iterações, erro 8.56e-09 (inicial 1.38e+00); reequilibrio_EOB RS (η = 0.05): necessário, convergiu em 7 iterações, erro 8.80e-10 (inicial 8.07e+01); reequilibrio_EOB RB (η = 0.05): necessário, convergiu em 8 iterações, erro 8.62e-10 (inicial 1.91e+03)</t>
+          <t>Σ coeficientes técnicos de cada coluna (inclui latentes)</t>
         </is>
       </c>
       <c r="F317" t="inlineStr">
@@ -48182,7 +49147,7 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>roteamento_vendas_geracao_igual_E</t>
+          <t>RAS_convergencia</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
@@ -48191,14 +49156,14 @@
         </is>
       </c>
       <c r="C318" s="2" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>22</v>
       </c>
       <c r="D318" s="2" t="n">
-        <v>1e-06</v>
+        <v>20000</v>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Σ vendas da geração de r dentro do bloco = E_r = F_r − T_r − G_r</t>
+          <t>linhas RS S38: necessário, convergiu em 22 iterações, erro 4.98e-09 (inicial 4.21e-01); linhas RB S38: necessário, convergiu em 21 iterações, erro 8.56e-09 (inicial 1.38e+00); reequilibrio_EOB RS (η = 0.05): necessário, convergiu em 7 iterações, erro 8.80e-10 (inicial 8.07e+01); reequilibrio_EOB RB (η = 0.05): necessário, convergiu em 8 iterações, erro 8.62e-10 (inicial 1.91e+03)</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
@@ -48210,7 +49175,7 @@
     <row r="319">
       <c r="A319" t="inlineStr">
         <is>
-          <t>roteamento_vendas_transmissao_igual_T</t>
+          <t>roteamento_vendas_geracao_igual_E</t>
         </is>
       </c>
       <c r="B319" t="inlineStr">
@@ -48219,14 +49184,14 @@
         </is>
       </c>
       <c r="C319" s="2" t="n">
-        <v>0</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="D319" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E319" t="inlineStr">
         <is>
-          <t>Σ vendas da transmissão de r dentro do bloco = T_r</t>
+          <t>Σ vendas da geração de r dentro do bloco = E_r = F_r − T_r − G_r</t>
         </is>
       </c>
       <c r="F319" t="inlineStr">
@@ -48238,7 +49203,7 @@
     <row r="320">
       <c r="A320" t="inlineStr">
         <is>
-          <t>roteamento_geracao_e_transmissao_nao_vendem_fora</t>
+          <t>roteamento_vendas_transmissao_igual_T</t>
         </is>
       </c>
       <c r="B320" t="inlineStr">
@@ -48254,7 +49219,7 @@
       </c>
       <c r="E320" t="inlineStr">
         <is>
-          <t>Σ |vendas| da geração e da transmissão fora do bloco e à demanda final (Seção 6.4)</t>
+          <t>Σ vendas da transmissão de r dentro do bloco = T_r</t>
         </is>
       </c>
       <c r="F320" t="inlineStr">
@@ -48266,7 +49231,7 @@
     <row r="321">
       <c r="A321" t="inlineStr">
         <is>
-          <t>roteamento_fracao_transmissao</t>
+          <t>roteamento_geracao_e_transmissao_nao_vendem_fora</t>
         </is>
       </c>
       <c r="B321" t="inlineStr">
@@ -48275,14 +49240,14 @@
         </is>
       </c>
       <c r="C321" s="2" t="n">
-        <v>8.173395242890144e-17</v>
+        <v>0</v>
       </c>
       <c r="D321" s="2" t="n">
-        <v>1e-09</v>
+        <v>1e-06</v>
       </c>
       <c r="E321" t="inlineStr">
         <is>
-          <t>fração da transmissão paga pela distribuição e pela geração das regiões desagregadas (o S38 agregado de região não desagregada recebe a sua parte inteira)</t>
+          <t>Σ |vendas| da geração e da transmissão fora do bloco e à demanda final (Seção 6.4)</t>
         </is>
       </c>
       <c r="F321" t="inlineStr">
@@ -48294,7 +49259,7 @@
     <row r="322">
       <c r="A322" t="inlineStr">
         <is>
-          <t>bloco_fluxos_regionais_preservados</t>
+          <t>roteamento_fracao_transmissao</t>
         </is>
       </c>
       <c r="B322" t="inlineStr">
@@ -48303,14 +49268,14 @@
         </is>
       </c>
       <c r="C322" s="2" t="n">
-        <v>1.455191522836685e-11</v>
+        <v>8.173395242890144e-17</v>
       </c>
       <c r="D322" s="2" t="n">
-        <v>1e-06</v>
+        <v>1e-09</v>
       </c>
       <c r="E322" t="inlineStr">
         <is>
-          <t>os fluxos alvo→alvo entre as regiões (ex.: RS→RS, RS→RB, RB→RS, RB→RB) são os da original</t>
+          <t>fração da transmissão paga pela distribuição e pela geração das regiões desagregadas (o S38 agregado de região não desagregada recebe a sua parte inteira)</t>
         </is>
       </c>
       <c r="F322" t="inlineStr">
@@ -48322,7 +49287,7 @@
     <row r="323">
       <c r="A323" t="inlineStr">
         <is>
-          <t>subsetores_latentes</t>
+          <t>bloco_fluxos_regionais_preservados</t>
         </is>
       </c>
       <c r="B323" t="inlineStr">
@@ -48331,14 +49296,14 @@
         </is>
       </c>
       <c r="C323" s="2" t="n">
-        <v>2</v>
+        <v>1.455191522836685e-11</v>
       </c>
       <c r="D323" s="2" t="n">
-        <v>0</v>
+        <v>1e-06</v>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>colunas de coeficientes guardadas à parte: RS_S38_SOL, RS_S38_PET</t>
+          <t>os fluxos alvo→alvo entre as regiões (ex.: RS→RS, RS→RB, RB→RS, RB→RB) são os da original</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
@@ -48350,7 +49315,7 @@
     <row r="324">
       <c r="A324" t="inlineStr">
         <is>
-          <t>piso_vbp_combustivel</t>
+          <t>subsetores_latentes</t>
         </is>
       </c>
       <c r="B324" t="inlineStr">
@@ -48359,14 +49324,14 @@
         </is>
       </c>
       <c r="C324" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="D324" s="2" t="n">
         <v>0</v>
       </c>
       <c r="E324" t="inlineStr">
         <is>
-          <t>VBP ≥ combustível ÷ κ (κ = 0.7); RS_S38_BIO: combustível/VBP = 0.0248; RS_S38_CAR: combustível/VBP = 0.0212; RS_S38_GN: combustível/VBP = 0.7000; RB_S38_BIO: combustível/VBP = 0.0198; RB_S38_CAR: combustível/VBP = 0.1044; RB_S38_GN: combustível/VBP = 0.7000; RB_S38_PET: combustível/VBP = 0.7000</t>
+          <t>colunas de coeficientes guardadas à parte: RS_S38_SOL, RS_S38_PET</t>
         </is>
       </c>
       <c r="F324" t="inlineStr">
@@ -48378,7 +49343,7 @@
     <row r="325">
       <c r="A325" t="inlineStr">
         <is>
-          <t>EOB_minimo_eta</t>
+          <t>piso_vbp_combustivel</t>
         </is>
       </c>
       <c r="B325" t="inlineStr">
@@ -48387,14 +49352,14 @@
         </is>
       </c>
       <c r="C325" s="2" t="n">
-        <v>0.04999999999999995</v>
+        <v>0</v>
       </c>
       <c r="D325" s="2" t="n">
-        <v>0.05</v>
+        <v>0</v>
       </c>
       <c r="E325" t="inlineStr">
         <is>
-          <t>EOB ≥ η × VBP (η = 0.05; tolerância absoluta 1e-06 R$ mi) em todo subsetor com produção</t>
+          <t>VBP ≥ combustível ÷ κ (κ = 0.7); RS_S38_BIO: combustível/VBP = 0.0248; RS_S38_CAR: combustível/VBP = 0.0212; RS_S38_GN: combustível/VBP = 0.7000; RB_S38_BIO: combustível/VBP = 0.0198; RB_S38_CAR: combustível/VBP = 0.1044; RB_S38_GN: combustível/VBP = 0.7000; RB_S38_PET: combustível/VBP = 0.7000</t>
         </is>
       </c>
       <c r="F325" t="inlineStr">
@@ -48406,7 +49371,7 @@
     <row r="326">
       <c r="A326" t="inlineStr">
         <is>
-          <t>reequilibrio_insumos_fixos</t>
+          <t>EOB_minimo_eta</t>
         </is>
       </c>
       <c r="B326" t="inlineStr">
@@ -48415,14 +49380,14 @@
         </is>
       </c>
       <c r="C326" s="2" t="n">
-        <v>0</v>
+        <v>0.04999999999999995</v>
       </c>
       <c r="D326" s="2" t="n">
-        <v>1e-06</v>
+        <v>0.05</v>
       </c>
       <c r="E326" t="inlineStr">
         <is>
-          <t>bloco, combustíveis, importações, remunerações e impostos sobre a produção iguais antes e depois do reequilíbrio</t>
+          <t>EOB ≥ η × VBP (η = 0.05; tolerância absoluta 1e-06 R$ mi) em todo subsetor com produção</t>
         </is>
       </c>
       <c r="F326" t="inlineStr">
@@ -48434,7 +49399,7 @@
     <row r="327">
       <c r="A327" t="inlineStr">
         <is>
-          <t>reequilibrio_soma_EOB_regiao</t>
+          <t>reequilibrio_insumos_fixos</t>
         </is>
       </c>
       <c r="B327" t="inlineStr">
@@ -48443,14 +49408,14 @@
         </is>
       </c>
       <c r="C327" s="2" t="n">
-        <v>2.728484105318785e-12</v>
+        <v>0</v>
       </c>
       <c r="D327" s="2" t="n">
         <v>1e-06</v>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Σ EOB dos subsetores de cada região = EOB original do setor-alvo; RB: Σ EOB = 103643.5529; RS: Σ EOB = 6737.4468</t>
+          <t>bloco, combustíveis, importações, remunerações e impostos sobre a produção iguais antes e depois do reequilíbrio</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
@@ -48462,7 +49427,7 @@
     <row r="328">
       <c r="A328" t="inlineStr">
         <is>
-          <t>insumos_nao_energeticos_minimo</t>
+          <t>reequilibrio_soma_EOB_regiao</t>
         </is>
       </c>
       <c r="B328" t="inlineStr">
@@ -48471,14 +49436,14 @@
         </is>
       </c>
       <c r="C328" s="2" t="n">
-        <v>0.05303108243990438</v>
+        <v>2.728484105318785e-12</v>
       </c>
       <c r="D328" s="2" t="n">
-        <v>0.05</v>
+        <v>1e-06</v>
       </c>
       <c r="E328" t="inlineStr">
         <is>
-          <t>compras a setores fora do bloco, exceto combustíveis, ÷ VBP ≥ 0.05 em todo subsetor com produção</t>
+          <t>Σ EOB dos subsetores de cada região = EOB original do setor-alvo; RB: Σ EOB = 103643.5529; RS: Σ EOB = 6737.4468</t>
         </is>
       </c>
       <c r="F328" t="inlineStr">
@@ -48490,26 +49455,54 @@
     <row r="329">
       <c r="A329" t="inlineStr">
         <is>
+          <t>insumos_nao_energeticos_minimo</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>OK</t>
+        </is>
+      </c>
+      <c r="C329" s="2" t="n">
+        <v>0.05303108243990438</v>
+      </c>
+      <c r="D329" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="E329" t="inlineStr">
+        <is>
+          <t>compras a setores fora do bloco, exceto combustíveis, ÷ VBP ≥ 0.05 em todo subsetor com produção</t>
+        </is>
+      </c>
+      <c r="F329" t="inlineStr">
+        <is>
+          <t>v04_eta005</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
           <t>multiplicador_producao_subsetores</t>
         </is>
       </c>
-      <c r="B329" t="inlineStr">
+      <c r="B330" t="inlineStr">
         <is>
           <t>ALERTA</t>
         </is>
       </c>
-      <c r="C329" s="2" t="n">
+      <c r="C330" s="2" t="n">
         <v>2.85107614788437</v>
       </c>
-      <c r="D329" s="2" t="n">
+      <c r="D330" s="2" t="n">
         <v>2.2</v>
       </c>
-      <c r="E329" t="inlineStr">
+      <c r="E330" t="inlineStr">
         <is>
           <t>multiplicador de produção (Σ coluna de L, inclui latentes) ≤ 2.2: acima em RS_S38_GN (2.443), RS_S38_PET (2.851), RS_S38_GAS (2.395), RB_S38_PET (2.810)</t>
         </is>
       </c>
-      <c r="F329" t="inlineStr">
+      <c r="F330" t="inlineStr">
         <is>
           <t>v04_eta005</t>
         </is>
@@ -48520,7 +49513,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -48647,776 +49640,6 @@
       </c>
       <c r="I3" s="2" t="n">
         <v>208427.8922088759</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:J19"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="14" customWidth="1" min="3" max="3"/>
-    <col width="19" customWidth="1" min="4" max="4"/>
-    <col width="19" customWidth="1" min="5" max="5"/>
-    <col width="20" customWidth="1" min="6" max="6"/>
-    <col width="29" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="58" customWidth="1" min="9" max="9"/>
-    <col width="15" customWidth="1" min="10" max="10"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>regiao</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>item</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>modo</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>total_base</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>identificado</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>residuo</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>fator_reducao_identificados</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>preserva_total</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>observacao</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>versao</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>residuo</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>5838005.554368285</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>3862147.829013172</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>1975857.725355113</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H2" t="b">
-        <v>1</v>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>residuo</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>84518349.05662796</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>34828615.16214097</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>49689733.89448699</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H3" t="b">
-        <v>1</v>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>residuo</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>5838005.554368285</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>3862147.829013172</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>1975857.725355113</v>
-      </c>
-      <c r="G4" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H4" t="b">
-        <v>1</v>
-      </c>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>v04_P2</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>residuo</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>84518349.05662796</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>34828615.16214097</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>49689733.89448699</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>v04_P2</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>proporcional</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>5838005.554368285</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>3862147.829013172</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>1975857.725355113</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>v04_E2</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>proporcional</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>84518349.05662796</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>34828615.16214097</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>49689733.89448699</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>v04_E2</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>sem_residuo</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>5838005.554368285</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>3862147.829013172</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>1975857.725355113</v>
-      </c>
-      <c r="G8" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H8" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>NÃO PRESERVA o total da base: diferença = -1975857.7254</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>v04_E3</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>sem_residuo</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>84518349.05662796</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>34828615.16214097</v>
-      </c>
-      <c r="F9" s="2" t="n">
-        <v>49689733.89448699</v>
-      </c>
-      <c r="G9" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H9" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>NÃO PRESERVA o total da base: diferença = -49689733.8945</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>v04_E3</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>residuo</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>5838005.554368285</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>3862147.829013172</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>1975857.725355113</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>v04_E4</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>residuo</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>84518349.05662796</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>34828615.16214097</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>49689733.89448699</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>v04_E4</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>residuo</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>5838005.554368285</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>3862147.829013172</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>1975857.725355113</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>v04_gas4dist</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>residuo</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>84518349.05662796</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>34828615.16214097</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>49689733.89448699</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>v04_gas4dist</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>residuo</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>5838005.554368285</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>3862147.829013172</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>1975857.725355113</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H14" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>v04_rap_media</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>residuo</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>84518349.05662796</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>34828615.16214098</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>49689733.89448698</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>v04_rap_media</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>residuo</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>5838005.554368285</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>3862147.829013172</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>1975857.725355113</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>v04_k060</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>residuo</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>84518349.05662796</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>34828615.16214097</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>49689733.89448699</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>v04_k060</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>residuo</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>5838005.554368285</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>3862147.829013172</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>1975857.725355113</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>v04_eta005</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>co2e</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>residuo</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>84518349.05662796</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>34828615.16214097</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>49689733.89448699</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="H19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>v04_eta005</t>
-        </is>
       </c>
     </row>
   </sheetData>
@@ -51744,6 +51967,776 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="4" max="4"/>
+    <col width="19" customWidth="1" min="5" max="5"/>
+    <col width="20" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="58" customWidth="1" min="9" max="9"/>
+    <col width="15" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>regiao</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>item</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>modo</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>total_base</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>identificado</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>residuo</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>fator_reducao_identificados</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>preserva_total</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>observacao</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>versao</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>residuo</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>5838005.554368285</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>3862147.829013172</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>1975857.725355113</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H2" t="b">
+        <v>1</v>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>residuo</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>84518349.05662796</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>34828615.16214097</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>49689733.89448699</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H3" t="b">
+        <v>1</v>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>residuo</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>5838005.554368285</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>3862147.829013172</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>1975857.725355113</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H4" t="b">
+        <v>1</v>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>v04_P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>residuo</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>84518349.05662796</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>34828615.16214097</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>49689733.89448699</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>v04_P2</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>proporcional</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>5838005.554368285</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>3862147.829013172</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>1975857.725355113</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>v04_E2</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>proporcional</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>84518349.05662796</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>34828615.16214097</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>49689733.89448699</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>v04_E2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>sem_residuo</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>5838005.554368285</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>3862147.829013172</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>1975857.725355113</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>NÃO PRESERVA o total da base: diferença = -1975857.7254</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>v04_E3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>sem_residuo</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>84518349.05662796</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>34828615.16214097</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>49689733.89448699</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>NÃO PRESERVA o total da base: diferença = -49689733.8945</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>v04_E3</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>residuo</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>5838005.554368285</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>3862147.829013172</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>1975857.725355113</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>v04_E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>residuo</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>84518349.05662796</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>34828615.16214097</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>49689733.89448699</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>v04_E4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>residuo</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>5838005.554368285</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3862147.829013172</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>1975857.725355113</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>v04_gas4dist</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>residuo</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>84518349.05662796</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>34828615.16214097</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>49689733.89448699</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>v04_gas4dist</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>residuo</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>5838005.554368285</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>3862147.829013172</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>1975857.725355113</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>v04_rap_media</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>residuo</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>84518349.05662796</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>34828615.16214098</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>49689733.89448698</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>v04_rap_media</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>residuo</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>5838005.554368285</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>3862147.829013172</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>1975857.725355113</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>v04_k060</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>residuo</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>84518349.05662796</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>34828615.16214097</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>49689733.89448699</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>v04_k060</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>residuo</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>5838005.554368285</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>3862147.829013172</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>1975857.725355113</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>v04_eta005</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>RB</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>co2e</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>residuo</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>84518349.05662796</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>34828615.16214097</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>49689733.89448699</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>v04_eta005</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -55077,7 +56070,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:Z3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -55099,6 +56092,13 @@
     <col width="45" customWidth="1" min="17" max="17"/>
     <col width="27" customWidth="1" min="18" max="18"/>
     <col width="27" customWidth="1" min="19" max="19"/>
+    <col width="29" customWidth="1" min="20" max="20"/>
+    <col width="21" customWidth="1" min="21" max="21"/>
+    <col width="21" customWidth="1" min="22" max="22"/>
+    <col width="29" customWidth="1" min="23" max="23"/>
+    <col width="30" customWidth="1" min="24" max="24"/>
+    <col width="13" customWidth="1" min="25" max="25"/>
+    <col width="27" customWidth="1" min="26" max="26"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -55197,6 +56197,41 @@
           <t>das quais diretas com D18</t>
         </is>
       </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>Δ coeficiente de TUST (D18)</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>VA/VBP do espelho</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>EOB/VBP do espelho</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>VA/VBP implícito da latente</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>EOB/VBP implícito da latente</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>η da versão</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>EOB implícito abaixo de η</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -55264,6 +56299,27 @@
       <c r="S2" s="2" t="n">
         <v>0</v>
       </c>
+      <c r="T2" s="2" t="n">
+        <v>0.06610375478814945</v>
+      </c>
+      <c r="U2" s="2" t="n">
+        <v>0.6961982386009486</v>
+      </c>
+      <c r="V2" s="2" t="n">
+        <v>0.5518306678299485</v>
+      </c>
+      <c r="W2" s="2" t="n">
+        <v>0.6300944838127992</v>
+      </c>
+      <c r="X2" s="2" t="n">
+        <v>0.485726913041799</v>
+      </c>
+      <c r="Y2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z2" t="b">
+        <v>0</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -55330,6 +56386,27 @@
       </c>
       <c r="S3" s="2" t="n">
         <v>1055.33598848684</v>
+      </c>
+      <c r="T3" s="2" t="n">
+        <v>0.03068813186653718</v>
+      </c>
+      <c r="U3" s="2" t="n">
+        <v>0.1502083247521721</v>
+      </c>
+      <c r="V3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="W3" s="2" t="n">
+        <v>0.1195201928856349</v>
+      </c>
+      <c r="X3" s="2" t="n">
+        <v>0.06931186813346285</v>
+      </c>
+      <c r="Y3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="Z3" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -55338,6 +56415,768 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="15" customWidth="1" min="1" max="1"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="29" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="21" customWidth="1" min="6" max="6"/>
+    <col width="29" customWidth="1" min="7" max="7"/>
+    <col width="30" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="9" max="9"/>
+    <col width="27" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>versao</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>regiao</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>subsetor</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>Δ coeficiente de TUST (D18)</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>VA/VBP do espelho</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>EOB/VBP do espelho</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>VA/VBP implícito da latente</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>EOB/VBP implícito da latente</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>η da versão</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>EOB implícito abaixo de η</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>S38_SOL</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="n">
+        <v>0.06610375478814945</v>
+      </c>
+      <c r="E2" s="2" t="n">
+        <v>0.6961982386009486</v>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>0.5518306678299485</v>
+      </c>
+      <c r="G2" s="2" t="n">
+        <v>0.6300944838127992</v>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>0.485726913041799</v>
+      </c>
+      <c r="I2" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J2" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>v04</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>S38_PET</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="n">
+        <v>0.03068813186653718</v>
+      </c>
+      <c r="E3" s="2" t="n">
+        <v>0.1502083247521721</v>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G3" s="2" t="n">
+        <v>0.1195201928856349</v>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>0.06931186813346285</v>
+      </c>
+      <c r="I3" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J3" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>v04_P2</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>S38_SOL</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="n">
+        <v>0.09934462838142893</v>
+      </c>
+      <c r="E4" s="2" t="n">
+        <v>0.6441106239197206</v>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>0.4997430531487205</v>
+      </c>
+      <c r="G4" s="2" t="n">
+        <v>0.5447659955382917</v>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>0.4003984247672916</v>
+      </c>
+      <c r="I4" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J4" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>v04_P2</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>S38_PET</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="n">
+        <v>0.03068813186653718</v>
+      </c>
+      <c r="E5" s="2" t="n">
+        <v>0.1502083247521719</v>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>0.09999999999999996</v>
+      </c>
+      <c r="G5" s="2" t="n">
+        <v>0.1195201928856348</v>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>0.06931186813346278</v>
+      </c>
+      <c r="I5" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J5" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>v04_E2</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>S38_SOL</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="n">
+        <v>0.06610375478814945</v>
+      </c>
+      <c r="E6" s="2" t="n">
+        <v>0.6961982386009486</v>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>0.5518306678299485</v>
+      </c>
+      <c r="G6" s="2" t="n">
+        <v>0.6300944838127992</v>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>0.485726913041799</v>
+      </c>
+      <c r="I6" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>v04_E2</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>S38_PET</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="n">
+        <v>0.03068813186653718</v>
+      </c>
+      <c r="E7" s="2" t="n">
+        <v>0.1502083247521721</v>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G7" s="2" t="n">
+        <v>0.1195201928856349</v>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>0.06931186813346285</v>
+      </c>
+      <c r="I7" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>v04_E3</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>S38_SOL</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="n">
+        <v>0.06610375478814945</v>
+      </c>
+      <c r="E8" s="2" t="n">
+        <v>0.6961982386009486</v>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>0.5518306678299485</v>
+      </c>
+      <c r="G8" s="2" t="n">
+        <v>0.6300944838127992</v>
+      </c>
+      <c r="H8" s="2" t="n">
+        <v>0.485726913041799</v>
+      </c>
+      <c r="I8" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>v04_E3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>S38_PET</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="n">
+        <v>0.03068813186653718</v>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0.1502083247521721</v>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G9" s="2" t="n">
+        <v>0.1195201928856349</v>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>0.06931186813346285</v>
+      </c>
+      <c r="I9" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>v04_E4</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>S38_SOL</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="n">
+        <v>0.06610375478814945</v>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>0.6961982386009486</v>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>0.5518306678299485</v>
+      </c>
+      <c r="G10" s="2" t="n">
+        <v>0.6300944838127992</v>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>0.485726913041799</v>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>v04_E4</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>S38_PET</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="n">
+        <v>0.03068813186653718</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>0.1502083247521721</v>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G11" s="2" t="n">
+        <v>0.1195201928856349</v>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>0.06931186813346285</v>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>v04_gas4dist</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>S38_SOL</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="n">
+        <v>0.06610375478814945</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>0.6961982386009485</v>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>0.5518306678299484</v>
+      </c>
+      <c r="G12" s="2" t="n">
+        <v>0.6300944838127991</v>
+      </c>
+      <c r="H12" s="2" t="n">
+        <v>0.4857269130417989</v>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>v04_gas4dist</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>S38_PET</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="n">
+        <v>0.03068813186653718</v>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>0.150208324752172</v>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G13" s="2" t="n">
+        <v>0.1195201928856348</v>
+      </c>
+      <c r="H13" s="2" t="n">
+        <v>0.06931186813346282</v>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>v04_rap_media</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>S38_SOL</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="n">
+        <v>0.07397560971149922</v>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>0.6833244878484681</v>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>0.5350126033487481</v>
+      </c>
+      <c r="G14" s="2" t="n">
+        <v>0.6093488781369689</v>
+      </c>
+      <c r="H14" s="2" t="n">
+        <v>0.4610369936372489</v>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>v04_rap_media</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>S38_PET</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="n">
+        <v>0.03329434431314965</v>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>0.151391618870788</v>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G15" s="2" t="n">
+        <v>0.1180972745576384</v>
+      </c>
+      <c r="H15" s="2" t="n">
+        <v>0.06670565568685038</v>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>v04_k060</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>S38_SOL</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>0.06899028657973424</v>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>0.7006007029081677</v>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>0.5562331321371676</v>
+      </c>
+      <c r="G16" s="2" t="n">
+        <v>0.6316104163284334</v>
+      </c>
+      <c r="H16" s="2" t="n">
+        <v>0.4872428455574334</v>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J16" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>v04_k060</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>S38_PET</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>0.02630411302846044</v>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>0.1636596456120046</v>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="G17" s="2" t="n">
+        <v>0.1373555325835442</v>
+      </c>
+      <c r="H17" s="2" t="n">
+        <v>0.07369588697153956</v>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J17" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>v04_eta005</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>S38_SOL</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="n">
+        <v>0.06610375478814945</v>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>0.7021769626421873</v>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>0.5578093918711872</v>
+      </c>
+      <c r="G18" s="2" t="n">
+        <v>0.6360732078540379</v>
+      </c>
+      <c r="H18" s="2" t="n">
+        <v>0.4917056370830377</v>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J18" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>v04_eta005</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>RS</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>S38_PET</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="n">
+        <v>0.03068813186653718</v>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>0.100208324752172</v>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>0.05000000000000001</v>
+      </c>
+      <c r="G19" s="2" t="n">
+        <v>0.06952019288563484</v>
+      </c>
+      <c r="H19" s="2" t="n">
+        <v>0.01931186813346283</v>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="J19" t="b">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -56411,7 +58250,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -56493,7 +58332,7 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>E4 (Rodada 05, Seção 3.2): Refino de petróleo (Produção de combustíveis + Geração de eletricidade › Produção de combustíveis) — SEEG 13.0, Dados nacionais, aba Dados (https://seeg.eco.br/wp-content/uploads/2025/12/Dados-nacionais-13.0.xlsx; SHA-256 21fc49654828cdb2eb63c104f06ba19d08b7dd81229fd9bf8972d80834aff350); recorte em dados/externos/seeg/seeg13_2019_recorte_energia_v04.csv; scripts/rodada05_diagnostico_seeg.py; regra da E4 = instruções da Rodada 05, Seção 3.2 (referência 1812.1 mil t); 'Não alocado' não entra</t>
+          <t>HIPÓTESE (E4, sensibilidade; Rodada 05, Seção 3.2): a conta-satélite da NEREUS incluiria no S38 estas emissões do SEEG (indício do diagnóstico NEREUS × SEEG, não prova); se elas já estiverem nos setores de destino, a E4 as conta duas vezes (no S19-RS, por exemplo) — Refino de petróleo (Produção de combustíveis + Geração de eletricidade › Produção de combustíveis) — SEEG 13.0, Dados nacionais, aba Dados (https://seeg.eco.br/wp-content/uploads/2025/12/Dados-nacionais-13.0.xlsx; SHA-256 21fc49654828cdb2eb63c104f06ba19d08b7dd81229fd9bf8972d80834aff350); recorte em dados/externos/seeg/seeg13_2019_recorte_energia_v04.csv; scripts/rodada05_diagnostico_seeg.py; regra da E4 = instruções da Rodada 05, Seção 3.2 (referência 1812.1 mil t: confere (arredondamento a 0.1 mil t)); 'Não alocado' não entra</t>
         </is>
       </c>
     </row>
@@ -56524,7 +58363,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>E4 (Rodada 05, Seção 3.2): Produção de carvão mineral e outros — SEEG 13.0, Dados nacionais, aba Dados (https://seeg.eco.br/wp-content/uploads/2025/12/Dados-nacionais-13.0.xlsx; SHA-256 21fc49654828cdb2eb63c104f06ba19d08b7dd81229fd9bf8972d80834aff350); recorte em dados/externos/seeg/seeg13_2019_recorte_energia_v04.csv; scripts/rodada05_diagnostico_seeg.py; regra da E4 = instruções da Rodada 05, Seção 3.2 (referência 88.1 mil t); 'Não alocado' não entra</t>
+          <t>HIPÓTESE (E4, sensibilidade; Rodada 05, Seção 3.2): a conta-satélite da NEREUS incluiria no S38 estas emissões do SEEG (indício do diagnóstico NEREUS × SEEG, não prova); se elas já estiverem nos setores de destino, a E4 as conta duas vezes (no S19-RS, por exemplo) — Produção de carvão mineral e outros — SEEG 13.0, Dados nacionais, aba Dados (https://seeg.eco.br/wp-content/uploads/2025/12/Dados-nacionais-13.0.xlsx; SHA-256 21fc49654828cdb2eb63c104f06ba19d08b7dd81229fd9bf8972d80834aff350); recorte em dados/externos/seeg/seeg13_2019_recorte_energia_v04.csv; scripts/rodada05_diagnostico_seeg.py; regra da E4 = instruções da Rodada 05, Seção 3.2 (referência 88.1 mil t: confere (arredondamento a 0.1 mil t)); 'Não alocado' não entra</t>
         </is>
       </c>
     </row>
@@ -56617,7 +58456,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>E4 (Rodada 05, Seção 3.2): Refino de petróleo (Produção de combustíveis + Geração de eletricidade › Produção de combustíveis) — SEEG 13.0, Dados nacionais, aba Dados (https://seeg.eco.br/wp-content/uploads/2025/12/Dados-nacionais-13.0.xlsx; SHA-256 21fc49654828cdb2eb63c104f06ba19d08b7dd81229fd9bf8972d80834aff350); recorte em dados/externos/seeg/seeg13_2019_recorte_energia_v04.csv; scripts/rodada05_diagnostico_seeg.py; regra da E4 = instruções da Rodada 05, Seção 3.2 (referência 18088.8 mil t); 'Não alocado' não entra</t>
+          <t>HIPÓTESE (E4, sensibilidade; Rodada 05, Seção 3.2): a conta-satélite da NEREUS incluiria no S38 estas emissões do SEEG (indício do diagnóstico NEREUS × SEEG, não prova); se elas já estiverem nos setores de destino, a E4 as conta duas vezes (no S19-RS, por exemplo) — Refino de petróleo (Produção de combustíveis + Geração de eletricidade › Produção de combustíveis) — SEEG 13.0, Dados nacionais, aba Dados (https://seeg.eco.br/wp-content/uploads/2025/12/Dados-nacionais-13.0.xlsx; SHA-256 21fc49654828cdb2eb63c104f06ba19d08b7dd81229fd9bf8972d80834aff350); recorte em dados/externos/seeg/seeg13_2019_recorte_energia_v04.csv; scripts/rodada05_diagnostico_seeg.py; regra da E4 = instruções da Rodada 05, Seção 3.2 (referência 18088.8 mil t: a referência 18088.8 das instruções é a soma das parcelas já arredondadas (17329.1 + 759.7 = 18088.8); o valor exato é 18088.87 mil t (18088.9 arredondado), e é o que vai no valor_t); 'Não alocado' não entra</t>
         </is>
       </c>
     </row>
@@ -56648,7 +58487,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>E4 (Rodada 05, Seção 3.2): Exploração de petróleo e gás natural (Produção de combustíveis + Geração de eletricidade › Produção de combustíveis) — SEEG 13.0, Dados nacionais, aba Dados (https://seeg.eco.br/wp-content/uploads/2025/12/Dados-nacionais-13.0.xlsx; SHA-256 21fc49654828cdb2eb63c104f06ba19d08b7dd81229fd9bf8972d80834aff350); recorte em dados/externos/seeg/seeg13_2019_recorte_energia_v04.csv; scripts/rodada05_diagnostico_seeg.py; regra da E4 = instruções da Rodada 05, Seção 3.2 (referência 23499.2 mil t); 'Não alocado' não entra</t>
+          <t>HIPÓTESE (E4, sensibilidade; Rodada 05, Seção 3.2): a conta-satélite da NEREUS incluiria no S38 estas emissões do SEEG (indício do diagnóstico NEREUS × SEEG, não prova); se elas já estiverem nos setores de destino, a E4 as conta duas vezes (no S19-RS, por exemplo) — Exploração de petróleo e gás natural (Produção de combustíveis + Geração de eletricidade › Produção de combustíveis) — SEEG 13.0, Dados nacionais, aba Dados (https://seeg.eco.br/wp-content/uploads/2025/12/Dados-nacionais-13.0.xlsx; SHA-256 21fc49654828cdb2eb63c104f06ba19d08b7dd81229fd9bf8972d80834aff350); recorte em dados/externos/seeg/seeg13_2019_recorte_energia_v04.csv; scripts/rodada05_diagnostico_seeg.py; regra da E4 = instruções da Rodada 05, Seção 3.2 (referência 23499.2 mil t: confere (arredondamento a 0.1 mil t)); 'Não alocado' não entra</t>
         </is>
       </c>
     </row>
@@ -56679,7 +58518,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>E4 (Rodada 05, Seção 3.2): Produção de carvão mineral e outros — SEEG 13.0, Dados nacionais, aba Dados (https://seeg.eco.br/wp-content/uploads/2025/12/Dados-nacionais-13.0.xlsx; SHA-256 21fc49654828cdb2eb63c104f06ba19d08b7dd81229fd9bf8972d80834aff350); recorte em dados/externos/seeg/seeg13_2019_recorte_energia_v04.csv; scripts/rodada05_diagnostico_seeg.py; regra da E4 = instruções da Rodada 05, Seção 3.2 (referência 1155.4 mil t); 'Não alocado' não entra</t>
+          <t>HIPÓTESE (E4, sensibilidade; Rodada 05, Seção 3.2): a conta-satélite da NEREUS incluiria no S38 estas emissões do SEEG (indício do diagnóstico NEREUS × SEEG, não prova); se elas já estiverem nos setores de destino, a E4 as conta duas vezes (no S19-RS, por exemplo) — Produção de carvão mineral e outros — SEEG 13.0, Dados nacionais, aba Dados (https://seeg.eco.br/wp-content/uploads/2025/12/Dados-nacionais-13.0.xlsx; SHA-256 21fc49654828cdb2eb63c104f06ba19d08b7dd81229fd9bf8972d80834aff350); recorte em dados/externos/seeg/seeg13_2019_recorte_energia_v04.csv; scripts/rodada05_diagnostico_seeg.py; regra da E4 = instruções da Rodada 05, Seção 3.2 (referência 1155.4 mil t: confere (arredondamento a 0.1 mil t)); 'Não alocado' não entra</t>
         </is>
       </c>
     </row>
@@ -56750,7 +58589,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -57790,968 +59629,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:G33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="8" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="20" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>versao</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>regiao</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>subsetor</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>VBP</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>TUST</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>TUST / VBP</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>remuneracoes / VBP</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>S38_HID</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="n">
-        <v>2478.318234397699</v>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>511.3643184267204</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>0.2063352120519729</v>
-      </c>
-      <c r="G2" s="2" t="n">
-        <v>0.06691592618436512</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>S38_EOL</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="n">
-        <v>933.8642937913977</v>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>185.2022746789912</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>0.1983181881032072</v>
-      </c>
-      <c r="G3" s="2" t="n">
-        <v>0.06691592618436512</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>S38_SOL</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>S38_BIO</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="n">
-        <v>14.39610458122591</v>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>2.399314045532176</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>0.1666641161152124</v>
-      </c>
-      <c r="G5" s="2" t="n">
-        <v>0.06520851157769522</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>S38_CAR</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="n">
-        <v>675.0415899274054</v>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>92.31156187608121</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>0.1367494436691056</v>
-      </c>
-      <c r="G6" s="2" t="n">
-        <v>0.0654537245601737</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>S38_GN</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="n">
-        <v>48.96694328784385</v>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>6.138188599700058</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>0.1253537220736398</v>
-      </c>
-      <c r="G7" s="2" t="n">
-        <v>0.02007477785530953</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>S38_PET</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr"/>
-      <c r="G8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>S38_NUC</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr"/>
-      <c r="G9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>S38_HID</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="n">
-        <v>45236.76699106405</v>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>8578.497122829611</v>
-      </c>
-      <c r="F10" s="2" t="n">
-        <v>0.189635504334874</v>
-      </c>
-      <c r="G10" s="2" t="n">
-        <v>0.1384575223270457</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>S38_EOL</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>6555.543617866584</v>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>1134.414365639333</v>
-      </c>
-      <c r="F11" s="2" t="n">
-        <v>0.1730465742837225</v>
-      </c>
-      <c r="G11" s="2" t="n">
-        <v>0.1384575223270457</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>S38_SOL</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="n">
-        <v>969.0298002286172</v>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>103.3584063315243</v>
-      </c>
-      <c r="F12" s="2" t="n">
-        <v>0.1066617417824917</v>
-      </c>
-      <c r="G12" s="2" t="n">
-        <v>0.1384575223270457</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>S38_BIO</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="n">
-        <v>272.6706285168253</v>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>41.76637322175468</v>
-      </c>
-      <c r="F13" s="2" t="n">
-        <v>0.1531751822663858</v>
-      </c>
-      <c r="G13" s="2" t="n">
-        <v>0.1356358917117955</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>S38_CAR</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="n">
-        <v>2100.294455021196</v>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>263.9684706987219</v>
-      </c>
-      <c r="F14" s="2" t="n">
-        <v>0.1256816490981299</v>
-      </c>
-      <c r="G14" s="2" t="n">
-        <v>0.1235436406794368</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>S38_GN</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="n">
-        <v>10981.93425757629</v>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>1095.545089944344</v>
-      </c>
-      <c r="F15" s="2" t="n">
-        <v>0.09975884614211217</v>
-      </c>
-      <c r="G15" s="2" t="n">
-        <v>0.04153725669811374</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>S38_PET</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="n">
-        <v>4066.596731580632</v>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>46.54031439396415</v>
-      </c>
-      <c r="F16" s="2" t="n">
-        <v>0.01144453641850898</v>
-      </c>
-      <c r="G16" s="2" t="n">
-        <v>0.04153725669811372</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>v03</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>S38_NUC</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="n">
-        <v>2981.204148523032</v>
-      </c>
-      <c r="E17" s="2" t="n">
-        <v>380.2079171537242</v>
-      </c>
-      <c r="F17" s="2" t="n">
-        <v>0.1275350154541041</v>
-      </c>
-      <c r="G17" s="2" t="n">
-        <v>0.1384575223270457</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>S38_HID</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="n">
-        <v>2549.693654128071</v>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>471.3357766749352</v>
-      </c>
-      <c r="F18" s="2" t="n">
-        <v>0.1848597677261427</v>
-      </c>
-      <c r="G18" s="2" t="n">
-        <v>0.06504251030705867</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>S38_EOL</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="n">
-        <v>960.7595306562334</v>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>170.7050234681092</v>
-      </c>
-      <c r="F19" s="2" t="n">
-        <v>0.1776771585617387</v>
-      </c>
-      <c r="G19" s="2" t="n">
-        <v>0.06504251030705865</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>S38_SOL</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr"/>
-      <c r="G20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>S38_BIO</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="n">
-        <v>14.81071154844496</v>
-      </c>
-      <c r="E21" s="2" t="n">
-        <v>2.211500701920889</v>
-      </c>
-      <c r="F21" s="2" t="n">
-        <v>0.1493176539619451</v>
-      </c>
-      <c r="G21" s="2" t="n">
-        <v>0.06342935618341794</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>S38_CAR</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="n">
-        <v>694.4827481078984</v>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>85.08560363930458</v>
-      </c>
-      <c r="F22" s="2" t="n">
-        <v>0.1225165115636325</v>
-      </c>
-      <c r="G22" s="2" t="n">
-        <v>0.06366103180122638</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>S38_GN</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="n">
-        <v>48.96694328784385</v>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>5.657703885007092</v>
-      </c>
-      <c r="F23" s="2" t="n">
-        <v>0.115541291841503</v>
-      </c>
-      <c r="G23" s="2" t="n">
-        <v>0.0195127530921176</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>S38_PET</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr"/>
-      <c r="G24" s="2" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>RS</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>S38_NUC</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="2" t="inlineStr"/>
-      <c r="G25" s="2" t="inlineStr"/>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>S38_HID</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="n">
-        <v>46660.99212599756</v>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>7906.990101563006</v>
-      </c>
-      <c r="F26" s="2" t="n">
-        <v>0.1694561075815094</v>
-      </c>
-      <c r="G26" s="2" t="n">
-        <v>0.1345132085983258</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>S38_EOL</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="n">
-        <v>6761.937014537989</v>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>1045.614754163652</v>
-      </c>
-      <c r="F27" s="2" t="n">
-        <v>0.1546324303103693</v>
-      </c>
-      <c r="G27" s="2" t="n">
-        <v>0.1345132085983258</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>S38_SOL</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="n">
-        <v>999.538536590299</v>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>95.26772394686297</v>
-      </c>
-      <c r="F28" s="2" t="n">
-        <v>0.09531170681207289</v>
-      </c>
-      <c r="G28" s="2" t="n">
-        <v>0.1345132085983258</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>S38_BIO</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="n">
-        <v>281.255334907724</v>
-      </c>
-      <c r="E29" s="2" t="n">
-        <v>38.49698786559352</v>
-      </c>
-      <c r="F29" s="2" t="n">
-        <v>0.136875582744853</v>
-      </c>
-      <c r="G29" s="2" t="n">
-        <v>0.1318556299518232</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>S38_CAR</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="n">
-        <v>2166.419696778494</v>
-      </c>
-      <c r="E30" s="2" t="n">
-        <v>243.3055644892561</v>
-      </c>
-      <c r="F30" s="2" t="n">
-        <v>0.1123076774325196</v>
-      </c>
-      <c r="G30" s="2" t="n">
-        <v>0.1204664325288654</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>S38_GN</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="n">
-        <v>10981.93425757629</v>
-      </c>
-      <c r="E31" s="2" t="n">
-        <v>1009.788085019323</v>
-      </c>
-      <c r="F31" s="2" t="n">
-        <v>0.09194992988805079</v>
-      </c>
-      <c r="G31" s="2" t="n">
-        <v>0.04035396257949774</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>S38_PET</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="n">
-        <v>4066.596731580632</v>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>42.89723479155547</v>
-      </c>
-      <c r="F32" s="2" t="n">
-        <v>0.01054868176586614</v>
-      </c>
-      <c r="G32" s="2" t="n">
-        <v>0.04035396257949776</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>v04</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>RB</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>S38_NUC</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="n">
-        <v>3075.0637711953</v>
-      </c>
-      <c r="E33" s="2" t="n">
-        <v>350.4460273664763</v>
-      </c>
-      <c r="F33" s="2" t="n">
-        <v>0.1139638243112777</v>
-      </c>
-      <c r="G33" s="2" t="n">
-        <v>0.1345132085983258</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>
--- a/resultados/rodada05/quadro_subsetores_v04.xlsx
+++ b/resultados/rodada05/quadro_subsetores_v04.xlsx
@@ -439,7 +439,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="140" customWidth="1" min="1" max="1"/>
@@ -469,19 +469,26 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Abas: v03_x_v04 (comparativo por subsetor), passos_v03_v04 (efeito de D17 e D18), d18_latentes (τ_RS, p_k, coeficiente de TUST e multiplicadores das latentes sem e com a D18), tust_latentes_versoes, realocacao_E4 (valores movidos na variante _E4), insumos_nao_energeticos (T12), tust_geracao, pisos_vbp, reequilibrio_RAS, reequilibrio_insumos, variantes_resumo e variantes_subsetores, gas_por_comprador e gas_por_grupo, checagens de todas as versões, niveis_emissoes.</t>
+          <t>Abas: v03_x_v04 (comparativo por subsetor), passos_v03_v04 (efeito de D17 e D18), d18_latentes (τ_RS, p_k, coeficiente de TUST e multiplicadores das latentes sem e com a D18; EOB/VBP implícito das latentes), d18_eob_implicito_versoes (o mesmo nas 9 versões; o PET-RS latente fica abaixo de η), tust_latentes_versoes, realocacao_E4 (valores movidos na variante _E4), insumos_nao_energeticos (T12), tust_geracao, pisos_vbp, reequilibrio_RAS, reequilibrio_insumos, variantes_resumo e variantes_subsetores, gas_por_comprador e gas_por_grupo, checagens de todas as versões, niveis_emissoes.</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GWh (D8): Brasil pelo BEN 2020 (Tabela 5.4), RS pelo ONS, RB = Brasil − RS.</t>
+          <t>realocacao_E4: sai de DIS e GAS só a parte de resíduo da E1, na proporção do resíduo de cada um (= do VBP); o SF₆, nível identificado na E1, fica. O que sobra em DIS + GAS = resíduo não movido + SF₆ do DIS; é esse total que corresponde à sobra de referência das instruções (Seção 3.2).</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>GWh (D8): Brasil pelo BEN 2020 (Tabela 5.4), RS pelo ONS, RB = Brasil − RS.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
         <is>
           <t>Gerado por scripts/rodada05_mip.py.</t>
         </is>
